--- a/web/files/港岛-香港仔及鸭脷洲-扬海.xlsx
+++ b/web/files/港岛-香港仔及鸭脷洲-扬海.xlsx
@@ -42542,11 +42542,32 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>37&amp;38</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>A | 1235呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr"/>
+      <c r="E6" s="21" t="inlineStr"/>
+      <c r="F6" s="21" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr"/>
+      <c r="H6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>B | 594呎 (2房)
 $1678万
@@ -42554,7 +42575,7 @@
 (24年-05月-27日)</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 749呎 (3房)
 $2413万
@@ -42562,8 +42583,8 @@
 (24年-04月-26日)</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr"/>
-      <c r="F6" s="20" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr"/>
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>E | 553呎 (2房)
 $1726万
@@ -42571,7 +42592,7 @@
 (24年-06月-12日)</t>
         </is>
       </c>
-      <c r="G6" s="20" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>F | 343呎 (1房)
 $1216万
@@ -42579,7 +42600,7 @@
 (21年-09月-20日)</t>
         </is>
       </c>
-      <c r="H6" s="20" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>G | 470呎 (2房)
 $1707万
@@ -42587,27 +42608,6 @@
 (22年-05月-27日)</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>37&amp;38</t>
-        </is>
-      </c>
-      <c r="B7" s="23" t="inlineStr">
-        <is>
-          <t>A | 1235呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="21" t="inlineStr"/>
-      <c r="D7" s="21" t="inlineStr"/>
-      <c r="E7" s="21" t="inlineStr"/>
-      <c r="F7" s="21" t="inlineStr"/>
-      <c r="G7" s="21" t="inlineStr"/>
-      <c r="H7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">

--- a/web/files/港岛-香港仔及鸭脷洲-扬海.xlsx
+++ b/web/files/港岛-香港仔及鸭脷洲-扬海.xlsx
@@ -42542,10 +42542,59 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 594呎 (2房)
+$1678万
+$28,251/呎
+(24年-05月-27日)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 749呎 (3房)
+$2413万
+$32,213/呎
+(24年-04月-26日)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>E | 553呎 (2房)
+$1726万
+$31,211/呎
+(24年-06月-12日)</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>F | 343呎 (1房)
+$1216万
+$35,464/呎
+(21年-09月-20日)</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr">
+        <is>
+          <t>G | 470呎 (2房)
+$1707万
+$36,317/呎
+(22年-05月-27日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>37&amp;38</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>A | 1235呎 (3房)
 -
@@ -42553,61 +42602,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr"/>
-      <c r="D6" s="21" t="inlineStr"/>
-      <c r="E6" s="21" t="inlineStr"/>
-      <c r="F6" s="21" t="inlineStr"/>
-      <c r="G6" s="21" t="inlineStr"/>
-      <c r="H6" s="21" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr"/>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>B | 594呎 (2房)
-$1678万
-$28,251/呎
-(24年-05月-27日)</t>
-        </is>
-      </c>
-      <c r="D7" s="20" t="inlineStr">
-        <is>
-          <t>C | 749呎 (3房)
-$2413万
-$32,213/呎
-(24年-04月-26日)</t>
-        </is>
-      </c>
+      <c r="C7" s="21" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr"/>
       <c r="E7" s="21" t="inlineStr"/>
-      <c r="F7" s="20" t="inlineStr">
-        <is>
-          <t>E | 553呎 (2房)
-$1726万
-$31,211/呎
-(24年-06月-12日)</t>
-        </is>
-      </c>
-      <c r="G7" s="20" t="inlineStr">
-        <is>
-          <t>F | 343呎 (1房)
-$1216万
-$35,464/呎
-(21年-09月-20日)</t>
-        </is>
-      </c>
-      <c r="H7" s="20" t="inlineStr">
-        <is>
-          <t>G | 470呎 (2房)
-$1707万
-$36,317/呎
-(22年-05月-27日)</t>
-        </is>
-      </c>
+      <c r="F7" s="21" t="inlineStr"/>
+      <c r="G7" s="21" t="inlineStr"/>
+      <c r="H7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">

--- a/web/files/港岛-香港仔及鸭脷洲-扬海.xlsx
+++ b/web/files/港岛-香港仔及鸭脷洲-扬海.xlsx
@@ -8657,7 +8657,7 @@
         </is>
       </c>
       <c r="E175" s="4" t="n">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="F175" s="3" t="inlineStr">
         <is>
@@ -8673,7 +8673,7 @@
         <v>38522400</v>
       </c>
       <c r="I175" s="5" t="n">
-        <v>40938</v>
+        <v>40894</v>
       </c>
       <c r="J175" s="3" t="inlineStr">
         <is>
@@ -28483,7 +28483,7 @@
           <t>A | 1848呎 (4+房)
 $13900万
 $75,216/呎
-(22年-02月)</t>
+(22年-02月-20日)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
@@ -28491,7 +28491,7 @@
           <t>B | 1102呎 (3房)
 $4972万
 $45,120/呎
-(24年-04月)</t>
+(24年-04月-08日)</t>
         </is>
       </c>
       <c r="D5" s="21" t="inlineStr"/>
@@ -28517,7 +28517,7 @@
           <t>B | 934呎 (3房)
 $4522万
 $48,415/呎
-(22年-02月)</t>
+(22年-02月-14日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -28525,7 +28525,7 @@
           <t>C | 524呎 (2房)
 $1872万
 $35,730/呎
-(21年-10月)</t>
+(21年-10月-10日)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -28533,7 +28533,7 @@
           <t>D | 751呎 (3房)
 $2360万
 $31,431/呎
-(23年-12月)</t>
+(23年-12月-26日)</t>
         </is>
       </c>
       <c r="F6" s="20" t="inlineStr">
@@ -28541,7 +28541,7 @@
           <t>E | 496呎 (2房)
 $1800万
 $36,293/呎
-(21年-10月)</t>
+(21年-10月-04日)</t>
         </is>
       </c>
     </row>
@@ -28564,7 +28564,7 @@
           <t>B | 934呎 (3房)
 $4477万
 $47,936/呎
-(22年-02月)</t>
+(22年-02月-09日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -28572,7 +28572,7 @@
           <t>C | 524呎 (2房)
 $1867万
 $35,623/呎
-(22年-02月)</t>
+(22年-02月-10日)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -28580,7 +28580,7 @@
           <t>D | 751呎 (3房)
 $2769万
 $36,867/呎
-(22年-05月)</t>
+(22年-05月-17日)</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
@@ -28588,7 +28588,7 @@
           <t>E | 496呎 (2房)
 $1795万
 $36,184/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
     </row>
@@ -28603,7 +28603,7 @@
           <t>A | 1299呎 (4+房)
 $7469万
 $57,500/呎
-(21年-09月)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -28611,7 +28611,7 @@
           <t>B | 934呎 (3房)
 $4167万
 $44,615/呎
-(24年-04月)</t>
+(24年-04月-07日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -28619,7 +28619,7 @@
           <t>C | 524呎 (2房)
 $1861万
 $35,518/呎
-(22年-02月)</t>
+(22年-02月-10日)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -28627,7 +28627,7 @@
           <t>D | 751呎 (3房)
 $2312万
 $30,784/呎
-(23年-12月)</t>
+(23年-12月-18日)</t>
         </is>
       </c>
       <c r="F8" s="20" t="inlineStr">
@@ -28635,7 +28635,7 @@
           <t>E | 496呎 (2房)
 $1789万
 $36,076/呎
-(21年-10月)</t>
+(21年-10月-04日)</t>
         </is>
       </c>
     </row>
@@ -28650,7 +28650,7 @@
           <t>A | 1299呎 (4+房)
 $6300万
 $48,499/呎
-(23年-04月)</t>
+(23年-04月-20日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -28658,7 +28658,7 @@
           <t>B | 934呎 (3房)
 $4360万
 $46,681/呎
-(23年-04月)</t>
+(23年-04月-25日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -28666,7 +28666,7 @@
           <t>C | 524呎 (2房)
 $1925万
 $36,740/呎
-(21年-11月)</t>
+(21年-11月-10日)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -28674,7 +28674,7 @@
           <t>D | 751呎 (3房)
 $2760万
 $36,758/呎
-(21年-10月)</t>
+(21年-10月-04日)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -28682,7 +28682,7 @@
           <t>E | 496呎 (2房)
 $1511万
 $30,465/呎
-(24年-05月)</t>
+(24年-05月-05日)</t>
         </is>
       </c>
     </row>
@@ -28697,7 +28697,7 @@
           <t>A | 1299呎 (4+房)
 $6174万
 $47,530/呎
-(24年-01月)</t>
+(24年-01月-11日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -28705,7 +28705,7 @@
           <t>B | 934呎 (3房)
 $4282万
 $45,843/呎
-(23年-02月)</t>
+(23年-02月-21日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -28713,7 +28713,7 @@
           <t>C | 524呎 (2房)
 $1866万
 $35,605/呎
-(23年-05月)</t>
+(23年-05月-08日)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -28721,7 +28721,7 @@
           <t>D | 751呎 (3房)
 $2613万
 $34,798/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -28729,7 +28729,7 @@
           <t>E | 496呎 (2房)
 $1669万
 $33,647/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
     </row>
@@ -28744,7 +28744,7 @@
           <t>A | 1299呎 (4+房)
 $6240万
 $48,037/呎
-(21年-09月)</t>
+(21年-09月-20日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -28752,7 +28752,7 @@
           <t>B | 934呎 (3房)
 $4278万
 $45,798/呎
-(21年-09月)</t>
+(21年-09月-10日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -28760,7 +28760,7 @@
           <t>C | 524呎 (2房)
 $1817万
 $34,678/呎
-(22年-05月)</t>
+(22年-05月-17日)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -28768,7 +28768,7 @@
           <t>D | 751呎 (3房)
 $2736万
 $36,429/呎
-(21年-09月)</t>
+(21年-09月-10日)</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
@@ -28776,7 +28776,7 @@
           <t>E | 496呎 (2房)
 $1664万
 $33,547/呎
-(21年-09月)</t>
+(21年-09月-10日)</t>
         </is>
       </c>
     </row>
@@ -28791,7 +28791,7 @@
           <t>A | 1299呎 (4+房)
 $6180万
 $47,575/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -28799,7 +28799,7 @@
           <t>B | 934呎 (3房)
 $4235万
 $45,345/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -28807,7 +28807,7 @@
           <t>C | 524呎 (2房)
 $1812万
 $34,573/呎
-(23年-03月)</t>
+(23年-03月-09日)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -28815,7 +28815,7 @@
           <t>D | 751呎 (3房)
 $2728万
 $36,320/呎
-(21年-10月)</t>
+(21年-10月-04日)</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
@@ -28823,7 +28823,7 @@
           <t>E | 496呎 (2房)
 $1659万
 $33,445/呎
-(21年-10月)</t>
+(21年-10月-04日)</t>
         </is>
       </c>
     </row>
@@ -28838,7 +28838,7 @@
           <t>A | 1299呎 (4+房)
 $6138万
 $47,252/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -28846,7 +28846,7 @@
           <t>B | 934呎 (3房)
 $4193万
 $44,896/呎
-(21年-10月)</t>
+(21年-10月-04日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -28854,7 +28854,7 @@
           <t>C | 524呎 (2房)
 $1806万
 $34,470/呎
-(23年-05月)</t>
+(23年-05月-24日)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -28862,7 +28862,7 @@
           <t>D | 751呎 (3房)
 $2331万
 $31,039/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
@@ -28870,7 +28870,7 @@
           <t>E | 496呎 (2房)
 $1694万
 $34,159/呎
-(21年-09月)</t>
+(21年-09月-23日)</t>
         </is>
       </c>
     </row>
@@ -28885,7 +28885,7 @@
           <t>A | 1299呎 (4+房)
 $5716万
 $44,004/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -28893,7 +28893,7 @@
           <t>B | 934呎 (3房)
 $3954万
 $42,334/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -28901,7 +28901,7 @@
           <t>C | 524呎 (2房)
 $1508万
 $28,783/呎
-(24年-02月)</t>
+(24年-02月-19日)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -28909,7 +28909,7 @@
           <t>D | 751呎 (3房)
 $2711万
 $36,103/呎
-(21年-10月)</t>
+(21年-10月-06日)</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -28917,7 +28917,7 @@
           <t>E | 496呎 (2房)
 $1689万
 $34,057/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
     </row>
@@ -28932,7 +28932,7 @@
           <t>A | 1299呎 (4+房)
 $5328万
 $41,016/呎
-(24年-04月)</t>
+(24年-04月-16日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -28940,7 +28940,7 @@
           <t>B | 934呎 (3房)
 $4016万
 $43,000/呎
-(21年-10月)</t>
+(21年-10月-10日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -28948,7 +28948,7 @@
           <t>C | 524呎 (2房)
 $1885万
 $35,979/呎
-(21年-10月)</t>
+(21年-10月-19日)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -28956,7 +28956,7 @@
           <t>D | 751呎 (3房)
 $2655万
 $35,353/呎
-(21年-09月)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
@@ -28964,7 +28964,7 @@
           <t>E | 496呎 (2房)
 $1604万
 $32,339/呎
-(21年-09月)</t>
+(21年-09月-20日)</t>
         </is>
       </c>
     </row>
@@ -28979,7 +28979,7 @@
           <t>A | 1299呎 (4+房)
 $5680万
 $43,726/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -28987,7 +28987,7 @@
           <t>B | 934呎 (3房)
 $3960万
 $42,402/呎
-(21年-09月)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -28995,7 +28995,7 @@
           <t>C | 524呎 (2房)
 $1880万
 $35,872/呎
-(21年-09月)</t>
+(21年-09月-17日)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -29003,7 +29003,7 @@
           <t>D | 751呎 (3房)
 $2695万
 $35,886/呎
-(21年-09月)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -29011,7 +29011,7 @@
           <t>E | 497呎 (2房)
 $1639万
 $32,981/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
     </row>
@@ -29026,7 +29026,7 @@
           <t>A | 1299呎 (4+房)
 $5389万
 $41,485/呎
-(21年-09月)</t>
+(21年-09月-20日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -29034,7 +29034,7 @@
           <t>B | 934呎 (3房)
 $3933万
 $42,107/呎
-(21年-09月)</t>
+(21年-09月-10日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -29042,7 +29042,7 @@
           <t>C | 524呎 (2房)
 $1495万
 $28,526/呎
-(23年-12月)</t>
+(23年-12月-28日)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -29050,7 +29050,7 @@
           <t>D | 751呎 (3房)
 $2559万
 $34,076/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -29058,7 +29058,7 @@
           <t>E | 497呎 (2房)
 $1594万
 $32,080/呎
-(21年-09月)</t>
+(21年-09月-20日)</t>
         </is>
       </c>
     </row>
@@ -29073,7 +29073,7 @@
           <t>A | 1299呎 (4+房)
 $5849万
 $45,030/呎
-(22年-02月)</t>
+(22年-02月-14日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -29081,7 +29081,7 @@
           <t>B | 934呎 (3房)
 $4206万
 $45,029/呎
-(22年-02月)</t>
+(22年-02月-14日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -29089,7 +29089,7 @@
           <t>C | 524呎 (2房)
 $1495万
 $28,526/呎
-(23年-11月)</t>
+(23年-11月-24日)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -29097,7 +29097,7 @@
           <t>D | 751呎 (3房)
 $2559万
 $34,076/呎
-(21年-10月)</t>
+(21年-10月-03日)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -29105,7 +29105,7 @@
           <t>E | 497呎 (2房)
 $1674万
 $33,685/呎
-(21年-09月)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
     </row>
@@ -29120,7 +29120,7 @@
           <t>A | 1299呎 (4+房)
 $5164万
 $39,758/呎
-(24年-04月)</t>
+(24年-04月-11日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -29128,7 +29128,7 @@
           <t>B | 934呎 (3房)
 $3951万
 $42,301/呎
-(23年-02月)</t>
+(23年-02月-19日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -29136,7 +29136,7 @@
           <t>C | 524呎 (2房)
 $1774万
 $33,858/呎
-(23年-03月)</t>
+(23年-03月-14日)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -29144,7 +29144,7 @@
           <t>D | 751呎 (3房)
 $2544万
 $33,874/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -29152,7 +29152,7 @@
           <t>E | 497呎 (2房)
 $1426万
 $28,700/呎
-(24年-05月)</t>
+(24年-05月-07日)</t>
         </is>
       </c>
     </row>
@@ -29167,7 +29167,7 @@
           <t>A | 1299呎 (4+房)
 $4880万
 $37,567/呎
-(25年-05月)</t>
+(25年-05月-29日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -29175,7 +29175,7 @@
           <t>B | 934呎 (3房)
 $3688万
 $39,481/呎
-(23年-12月)</t>
+(23年-12月-14日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -29183,7 +29183,7 @@
           <t>C | 524呎 (2房)
 $1481万
 $28,272/呎
-(23年-12月)</t>
+(23年-12月-19日)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -29191,7 +29191,7 @@
           <t>D | 751呎 (3房)
 $2663万
 $35,459/呎
-(21年-10月)</t>
+(21年-10月-07日)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -29199,7 +29199,7 @@
           <t>E | 497呎 (2房)
 $1580万
 $31,792/呎
-(21年-09月)</t>
+(21年-09月-23日)</t>
         </is>
       </c>
     </row>
@@ -29214,7 +29214,7 @@
           <t>A | 1299呎 (4+房)
 $5040万
 $38,800/呎
-(24年-07月)</t>
+(24年-07月-01日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -29222,7 +29222,7 @@
           <t>B | 934呎 (3房)
 $3974万
 $42,549/呎
-(21年-09月)</t>
+(21年-09月-17日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -29230,7 +29230,7 @@
           <t>C | 524呎 (2房)
 $1499万
 $28,609/呎
-(23年-12月)</t>
+(23年-12月-18日)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
@@ -29238,7 +29238,7 @@
           <t>D | 751呎 (3房)
 $2529万
 $33,669/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -29246,7 +29246,7 @@
           <t>E | 497呎 (2房)
 $1654万
 $33,286/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
     </row>
@@ -29261,7 +29261,7 @@
           <t>A | 1299呎 (4+房)
 $5238万
 $40,320/呎
-(21年-10月)</t>
+(21年-10月-06日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -29269,7 +29269,7 @@
           <t>B | 934呎 (3房)
 $3766万
 $40,322/呎
-(21年-10月)</t>
+(21年-10月-06日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -29277,7 +29277,7 @@
           <t>C | 524呎 (2房)
 $1473万
 $28,104/呎
-(23年-12月)</t>
+(23年-12月-18日)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -29285,7 +29285,7 @@
           <t>D | 751呎 (3房)
 $2521万
 $33,569/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -29293,7 +29293,7 @@
           <t>E | 497呎 (2房)
 $1620万
 $32,593/呎
-(21年-09月)</t>
+(21年-09月-20日)</t>
         </is>
       </c>
     </row>
@@ -29308,7 +29308,7 @@
           <t>A | 1299呎 (4+房)
 $5472万
 $42,125/呎
-(21年-10月)</t>
+(21年-10月-07日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -29316,7 +29316,7 @@
           <t>B | 934呎 (3房)
 $3747万
 $40,121/呎
-(21年-10月)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -29324,7 +29324,7 @@
           <t>C | 524呎 (2房)
 $1468万
 $28,020/呎
-(23年-12月)</t>
+(23年-12月-27日)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -29332,7 +29332,7 @@
           <t>D | 751呎 (3房)
 $2514万
 $33,469/呎
-(21年-09月)</t>
+(21年-09月-29日)</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -29340,7 +29340,7 @@
           <t>E | 497呎 (2房)
 $1605万
 $32,299/呎
-(21年-09月)</t>
+(21年-09月-29日)</t>
         </is>
       </c>
     </row>
@@ -29355,7 +29355,7 @@
           <t>A | 1299呎 (4+房)
 $4875万
 $37,529/呎
-(24年-04月)</t>
+(24年-04月-16日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -29363,7 +29363,7 @@
           <t>B | 934呎 (3房)
 $3505万
 $37,526/呎
-(24年-08月)</t>
+(24年-08月-12日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -29371,7 +29371,7 @@
           <t>C | 524呎 (2房)
 $1464万
 $27,937/呎
-(24年-03月)</t>
+(24年-03月-12日)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -29379,7 +29379,7 @@
           <t>D | 751呎 (3房)
 $2506万
 $33,369/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -29387,7 +29387,7 @@
           <t>E | 497呎 (2房)
 $1561万
 $31,417/呎
-(21年-09月)</t>
+(21年-09月-19日)</t>
         </is>
       </c>
     </row>
@@ -29402,7 +29402,7 @@
           <t>A | 1299呎 (4+房)
 $5365万
 $41,298/呎
-(21年-10月)</t>
+(21年-10月-10日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -29410,7 +29410,7 @@
           <t>B | 934呎 (3房)
 $3674万
 $39,331/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -29418,7 +29418,7 @@
           <t>C | 524呎 (2房)
 $1417万
 $27,044/呎
-(24年-03月)</t>
+(24年-03月-21日)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -29426,7 +29426,7 @@
           <t>D | 751呎 (3房)
 $2623万
 $34,931/呎
-(21年-09月)</t>
+(21年-09月-10日)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -29434,7 +29434,7 @@
           <t>E | 497呎 (2房)
 $1635万
 $32,889/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
     </row>
@@ -29449,7 +29449,7 @@
           <t>A | 1299呎 (4+房)
 $4704万
 $36,216/呎
-(25年-10月)</t>
+(25年-10月-07日)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -29457,7 +29457,7 @@
           <t>B | 934呎 (3房)
 $3819万
 $40,888/呎
-(21年-10月)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -29465,7 +29465,7 @@
           <t>C | 524呎 (2房)
 $1409万
 $26,885/呎
-(24年-03月)</t>
+(24年-03月-07日)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -29473,7 +29473,7 @@
           <t>D | 751呎 (3房)
 $2608万
 $34,723/呎
-(21年-10月)</t>
+(21年-10月-04日)</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
@@ -29481,7 +29481,7 @@
           <t>E | 497呎 (2房)
 $1625万
 $32,693/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
     </row>
@@ -29496,7 +29496,7 @@
           <t>A | 1299呎 (4+房)
 $4731万
 $36,423/呎
-(24年-03月)</t>
+(24年-03月-20日)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -29504,7 +29504,7 @@
           <t>B | 934呎 (3房)
 $3800万
 $40,685/呎
-(21年-10月)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -29512,7 +29512,7 @@
           <t>C | 524呎 (2房)
 $1405万
 $26,804/呎
-(24年-04月)</t>
+(24年-04月-04日)</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">
@@ -29520,7 +29520,7 @@
           <t>D | 751呎 (3房)
 $2476万
 $32,970/呎
-(21年-10月)</t>
+(21年-10月-04日)</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
@@ -29528,7 +29528,7 @@
           <t>E | 497呎 (2房)
 $1620万
 $32,596/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
     </row>
@@ -29543,7 +29543,7 @@
           <t>A | 1229呎 (4+房)
 $5430万
 $44,181/呎
-(24年-03月)</t>
+(24年-03月-21日)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -29551,7 +29551,7 @@
           <t>B | 874呎 (3房)
 $3861万
 $44,180/呎
-(23年-12月)</t>
+(23年-12月-21日)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -29559,7 +29559,7 @@
           <t>C | 487呎 (2房)
 $1694万
 $34,778/呎
-(22年-02月)</t>
+(22年-02月-14日)</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
@@ -29567,7 +29567,7 @@
           <t>D | 709呎 (3房)
 $2482万
 $35,000/呎
-(22年-02月)</t>
+(22年-02月-14日)</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
@@ -29575,7 +29575,7 @@
           <t>E | 461呎 (2房)
 $1567万
 $34,001/呎
-(22年-02月)</t>
+(22年-02月-13日)</t>
         </is>
       </c>
     </row>
@@ -29725,7 +29725,7 @@
           <t>A | 1902呎 (4+房)
 $13000万
 $68,349/呎
-(24年-06月)</t>
+(24年-06月-17日)</t>
         </is>
       </c>
       <c r="C5" s="23" t="inlineStr">
@@ -29741,7 +29741,7 @@
           <t>C | 1000呎 (3房)
 $4700万
 $47,000/呎
-(24年-06月)</t>
+(24年-06月-26日)</t>
         </is>
       </c>
       <c r="E5" s="21" t="inlineStr"/>
@@ -29759,7 +29759,7 @@
           <t>A | 1420呎 (4+房)
 $8557万
 $60,260/呎
-(26年-03月)</t>
+(26年-03月-04日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -29767,7 +29767,7 @@
           <t>B | 942呎 (3房)
 $4553万
 $48,334/呎
-(26年-03月)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -29775,7 +29775,7 @@
           <t>C | 589呎 (2房)
 $1981万
 $33,630/呎
-(21年-10月)</t>
+(21年-10月-06日)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -29783,7 +29783,7 @@
           <t>D | 481呎 (2房)
 $1602万
 $33,314/呎
-(21年-09月)</t>
+(21年-09月-29日)</t>
         </is>
       </c>
       <c r="F6" s="20" t="inlineStr">
@@ -29791,7 +29791,7 @@
           <t>E | 523呎 (2房)
 $1817万
 $34,733/呎
-(21年-09月)</t>
+(21年-09月-29日)</t>
         </is>
       </c>
       <c r="G6" s="20" t="inlineStr">
@@ -29799,7 +29799,7 @@
           <t>F | 464呎 (2房)
 $1386万
 $29,861/呎
-(24年-01月)</t>
+(24年-01月-13日)</t>
         </is>
       </c>
     </row>
@@ -29822,7 +29822,7 @@
           <t>B | 942呎 (3房)
 $4095万
 $43,471/呎
-(25年-10月)</t>
+(25年-10月-27日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -29830,7 +29830,7 @@
           <t>C | 589呎 (2房)
 $1975万
 $33,529/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -29838,7 +29838,7 @@
           <t>D | 481呎 (2房)
 $1678万
 $34,877/呎
-(21年-10月)</t>
+(21年-10月-04日)</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
@@ -29846,7 +29846,7 @@
           <t>E | 523呎 (2房)
 $1806万
 $34,527/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
@@ -29854,7 +29854,7 @@
           <t>F | 464呎 (2房)
 $1698万
 $36,586/呎
-(21年-10月)</t>
+(21年-10月-04日)</t>
         </is>
       </c>
     </row>
@@ -29869,7 +29869,7 @@
           <t>A | 1420呎 (4+房)
 $8520万
 $60,000/呎
-(21年-09月)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -29877,7 +29877,7 @@
           <t>B | 942呎 (3房)
 $4360万
 $46,283/呎
-(26年-07月)</t>
+(26年-07月-27日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -29885,7 +29885,7 @@
           <t>C | 589呎 (2房)
 $1969万
 $33,429/呎
-(21年-10月)</t>
+(21年-10月-04日)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -29893,7 +29893,7 @@
           <t>D | 481呎 (2房)
 $1673万
 $34,772/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="F8" s="20" t="inlineStr">
@@ -29901,7 +29901,7 @@
           <t>E | 524呎 (2房)
 $1887万
 $36,005/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -29909,7 +29909,7 @@
           <t>F | 464呎 (2房)
 $1638万
 $35,302/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
     </row>
@@ -29924,7 +29924,7 @@
           <t>A | 1420呎 (4+房)
 $7025万
 $49,470/呎
-(23年-11月)</t>
+(23年-11月-29日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -29932,7 +29932,7 @@
           <t>B | 942呎 (3房)
 $3651万
 $38,759/呎
-(25年-02月)</t>
+(25年-02月-11日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -29940,7 +29940,7 @@
           <t>C | 589呎 (2房)
 $1940万
 $32,934/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -29948,7 +29948,7 @@
           <t>D | 481呎 (2房)
 $1600万
 $33,270/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -29956,7 +29956,7 @@
           <t>E | 524呎 (2房)
 $1703万
 $32,498/呎
-(21年-09月)</t>
+(21年-09月-23日)</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -29964,7 +29964,7 @@
           <t>F | 464呎 (2房)
 $1614万
 $34,779/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
     </row>
@@ -29979,7 +29979,7 @@
           <t>A | 1420呎 (4+房)
 $6887万
 $48,500/呎
-(23年-11月)</t>
+(23年-11月-29日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -29987,7 +29987,7 @@
           <t>B | 942呎 (3房)
 $4085万
 $43,364/呎
-(23年-11月)</t>
+(23年-11月-29日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -29995,7 +29995,7 @@
           <t>C | 589呎 (2房)
 $2025万
 $34,376/呎
-(21年-10月)</t>
+(21年-10月-04日)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -30003,7 +30003,7 @@
           <t>D | 481呎 (2房)
 $1591万
 $33,069/呎
-(21年-09月)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -30011,7 +30011,7 @@
           <t>E | 524呎 (2房)
 $1686万
 $32,174/呎
-(21年-09月)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -30019,7 +30019,7 @@
           <t>F | 464呎 (2房)
 $1598万
 $34,434/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
     </row>
@@ -30034,7 +30034,7 @@
           <t>A | 1420呎 (4+房)
 $6929万
 $48,796/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -30042,7 +30042,7 @@
           <t>B | 941呎 (3房)
 $4168万
 $44,288/呎
-(21年-10月)</t>
+(21年-10月-07日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -30050,7 +30050,7 @@
           <t>C | 589呎 (2房)
 $2019万
 $34,273/呎
-(21年-10月)</t>
+(21年-10月-04日)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -30058,7 +30058,7 @@
           <t>D | 481呎 (2房)
 $1510万
 $31,400/呎
-(21年-09月)</t>
+(21年-09月-19日)</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
@@ -30066,7 +30066,7 @@
           <t>E | 524呎 (2房)
 $1678万
 $32,014/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
@@ -30074,7 +30074,7 @@
           <t>F | 464呎 (2房)
 $1640万
 $35,335/呎
-(21年-09月)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
     </row>
@@ -30089,7 +30089,7 @@
           <t>A | 1420呎 (4+房)
 $6958万
 $48,997/呎
-(21年-10月)</t>
+(21年-10月-10日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -30097,7 +30097,7 @@
           <t>B | 941呎 (3房)
 $3930万
 $41,762/呎
-(21年-09月)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -30105,7 +30105,7 @@
           <t>C | 589呎 (2房)
 $2013万
 $34,170/呎
-(21年-09月)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -30113,7 +30113,7 @@
           <t>D | 481呎 (2房)
 $1544万
 $32,091/呎
-(21年-09月)</t>
+(21年-09月-23日)</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
@@ -30121,7 +30121,7 @@
           <t>E | 524呎 (2房)
 $1735万
 $33,119/呎
-(21年-09月)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="G12" s="20" t="inlineStr">
@@ -30129,7 +30129,7 @@
           <t>F | 464呎 (2房)
 $1566万
 $33,759/呎
-(21年-09月)</t>
+(21年-09月-10日)</t>
         </is>
       </c>
     </row>
@@ -30144,7 +30144,7 @@
           <t>A | 1420呎 (4+房)
 $7009万
 $49,358/呎
-(21年-10月)</t>
+(21年-10月-06日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -30152,7 +30152,7 @@
           <t>B | 942呎 (3房)
 $4085万
 $43,370/呎
-(21年-10月)</t>
+(21年-10月-06日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -30160,7 +30160,7 @@
           <t>C | 589呎 (2房)
 $1971万
 $33,459/呎
-(21年-10月)</t>
+(21年-10月-06日)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -30168,7 +30168,7 @@
           <t>D | 481呎 (2房)
 $1561万
 $32,449/呎
-(21年-09月)</t>
+(21年-09月-19日)</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
@@ -30176,7 +30176,7 @@
           <t>E | 523呎 (2房)
 $1710万
 $32,689/呎
-(21年-09月)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
@@ -30184,7 +30184,7 @@
           <t>F | 464呎 (2房)
 $1559万
 $33,591/呎
-(21年-10月)</t>
+(21年-10月-06日)</t>
         </is>
       </c>
     </row>
@@ -30199,15 +30199,15 @@
           <t>A | 1420呎 (4+房)
 $6532万
 $46,002/呎
-(21年-10月)</t>
+(21年-10月-06日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>B | 941呎 (3房)
+          <t>B | 942呎 (3房)
 $3852万
-$40,938/呎
-(21年-10月)</t>
+$40,894/呎
+(21年-10月-04日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -30215,7 +30215,7 @@
           <t>C | 589呎 (2房)
 $1905万
 $32,346/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -30223,7 +30223,7 @@
           <t>D | 481呎 (2房)
 $1334万
 $27,731/呎
-(24年-05月)</t>
+(24年-05月-06日)</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -30231,7 +30231,7 @@
           <t>E | 524呎 (2房)
 $1620万
 $30,918/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
@@ -30239,7 +30239,7 @@
           <t>F | 464呎 (2房)
 $1299万
 $27,993/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
     </row>
@@ -30254,7 +30254,7 @@
           <t>A | 1420呎 (4+房)
 $6816万
 $48,000/呎
-(21年-09月)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -30262,7 +30262,7 @@
           <t>B | 942呎 (3房)
 $3905万
 $41,456/呎
-(21年-10月)</t>
+(21年-10月-10日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -30270,7 +30270,7 @@
           <t>C | 589呎 (2房)
 $1900万
 $32,250/呎
-(21年-10月)</t>
+(21年-10月-04日)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -30278,7 +30278,7 @@
           <t>D | 481呎 (2房)
 $1524万
 $31,679/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
@@ -30286,7 +30286,7 @@
           <t>E | 523呎 (2房)
 $1646万
 $31,475/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="G15" s="20" t="inlineStr">
@@ -30294,7 +30294,7 @@
           <t>F | 464呎 (2房)
 $1528万
 $32,931/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
     </row>
@@ -30309,7 +30309,7 @@
           <t>A | 1420呎 (4+房)
 $6404万
 $45,100/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -30317,7 +30317,7 @@
           <t>B | 942呎 (3房)
 $3695万
 $39,223/呎
-(26年-01月)</t>
+(26年-01月-13日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -30325,7 +30325,7 @@
           <t>C | 588呎 (2房)
 $1894万
 $32,211/呎
-(21年-09月)</t>
+(21年-09月-10日)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -30333,7 +30333,7 @@
           <t>D | 481呎 (2房)
 $1547万
 $32,159/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -30341,7 +30341,7 @@
           <t>E | 523呎 (2房)
 $1668万
 $31,888/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -30349,7 +30349,7 @@
           <t>F | 464呎 (2房)
 $1520万
 $32,766/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
     </row>
@@ -30364,7 +30364,7 @@
           <t>A | 1420呎 (4+房)
 $6107万
 $43,010/呎
-(21年-09月)</t>
+(21年-09月-29日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -30372,7 +30372,7 @@
           <t>B | 942呎 (3房)
 $3784万
 $40,167/呎
-(21年-10月)</t>
+(21年-10月-04日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -30380,7 +30380,7 @@
           <t>C | 588呎 (2房)
 $1888万
 $32,114/呎
-(21年-10月)</t>
+(21年-10月-03日)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -30388,7 +30388,7 @@
           <t>D | 481呎 (2房)
 $1542万
 $32,063/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -30396,7 +30396,7 @@
           <t>E | 523呎 (2房)
 $1422万
 $27,196/呎
-(24年-04月)</t>
+(24年-04月-16日)</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -30404,7 +30404,7 @@
           <t>F | 464呎 (2房)
 $1560万
 $33,621/呎
-(21年-10月)</t>
+(21年-10月-03日)</t>
         </is>
       </c>
     </row>
@@ -30419,7 +30419,7 @@
           <t>A | 1420呎 (4+房)
 $5900万
 $41,549/呎
-(23年-12月)</t>
+(23年-12月-04日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -30427,7 +30427,7 @@
           <t>B | 942呎 (3房)
 $3660万
 $38,854/呎
-(23年-11月)</t>
+(23年-11月-28日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -30435,7 +30435,7 @@
           <t>C | 589呎 (2房)
 $1888万
 $32,060/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -30443,7 +30443,7 @@
           <t>D | 481呎 (2房)
 $1469万
 $30,536/呎
-(21年-09月)</t>
+(21年-09月-20日)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -30451,7 +30451,7 @@
           <t>E | 523呎 (2房)
 $1580万
 $30,218/呎
-(21年-09月)</t>
+(21年-09月-20日)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -30459,7 +30459,7 @@
           <t>F | 464呎 (2房)
 $1513万
 $32,602/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
     </row>
@@ -30474,7 +30474,7 @@
           <t>A | 1420呎 (4+房)
 $6292万
 $44,308/呎
-(22年-06月)</t>
+(22年-06月-20日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -30482,7 +30482,7 @@
           <t>B | 942呎 (3房)
 $3652万
 $38,770/呎
-(24年-04月)</t>
+(24年-04月-24日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -30490,7 +30490,7 @@
           <t>C | 588呎 (2房)
 $1971万
 $33,517/呎
-(21年-10月)</t>
+(21年-10月-04日)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -30498,7 +30498,7 @@
           <t>D | 481呎 (2房)
 $1460万
 $30,355/呎
-(21年-09月)</t>
+(21年-09月-03日)</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -30506,7 +30506,7 @@
           <t>E | 523呎 (2房)
 $1565万
 $29,920/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -30514,7 +30514,7 @@
           <t>F | 464呎 (2房)
 $1535万
 $33,088/呎
-(21年-09月)</t>
+(21年-09月-10日)</t>
         </is>
       </c>
     </row>
@@ -30529,7 +30529,7 @@
           <t>A | 1420呎 (4+房)
 $5623万
 $39,600/呎
-(25年-09月)</t>
+(25年-09月-08日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -30537,7 +30537,7 @@
           <t>B | 942呎 (3房)
 $3627万
 $38,499/呎
-(25年-09月)</t>
+(25年-09月-08日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -30545,7 +30545,7 @@
           <t>C | 588呎 (2房)
 $1965万
 $33,416/呎
-(21年-09月)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -30553,7 +30553,7 @@
           <t>D | 481呎 (2房)
 $1528万
 $31,777/呎
-(21年-09月)</t>
+(21年-09月-23日)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -30561,7 +30561,7 @@
           <t>E | 523呎 (2房)
 $1638万
 $31,321/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
@@ -30569,7 +30569,7 @@
           <t>F | 465呎 (2房)
 $1568万
 $33,719/呎
-(21年-10月)</t>
+(21年-10月-04日)</t>
         </is>
       </c>
     </row>
@@ -30584,7 +30584,7 @@
           <t>A | 1420呎 (4+房)
 $6262万
 $44,101/呎
-(21年-10月)</t>
+(21年-10月-10日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -30592,7 +30592,7 @@
           <t>B | 942呎 (3房)
 $3887万
 $41,258/呎
-(21年-10月)</t>
+(21年-10月-10日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -30600,7 +30600,7 @@
           <t>C | 589呎 (2房)
 $1959万
 $33,261/呎
-(21年-10月)</t>
+(21年-10月-07日)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
@@ -30608,7 +30608,7 @@
           <t>D | 481呎 (2房)
 $1524万
 $31,684/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -30616,7 +30616,7 @@
           <t>E | 523呎 (2房)
 $1604万
 $30,670/呎
-(21年-09月)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr">
@@ -30624,7 +30624,7 @@
           <t>F | 465呎 (2房)
 $1563万
 $33,618/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
     </row>
@@ -30639,7 +30639,7 @@
           <t>A | 1420呎 (4+房)
 $6231万
 $43,881/呎
-(21年-10月)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -30647,7 +30647,7 @@
           <t>B | 942呎 (3房)
 $3867万
 $41,053/呎
-(21年-10月)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -30655,7 +30655,7 @@
           <t>C | 588呎 (2房)
 $1860万
 $31,635/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -30663,7 +30663,7 @@
           <t>D | 481呎 (2房)
 $1447万
 $30,084/呎
-(21年-09月)</t>
+(21年-09月-23日)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -30671,7 +30671,7 @@
           <t>E | 523呎 (2房)
 $1628万
 $31,133/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr">
@@ -30679,7 +30679,7 @@
           <t>F | 464呎 (2房)
 $1559万
 $33,591/呎
-(21年-10月)</t>
+(21年-10月-04日)</t>
         </is>
       </c>
     </row>
@@ -30694,7 +30694,7 @@
           <t>A | 1420呎 (4+房)
 $5905万
 $41,584/呎
-(21年-10月)</t>
+(21年-10月-10日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -30702,7 +30702,7 @@
           <t>B | 942呎 (3房)
 $3555万
 $37,738/呎
-(26年-04月)</t>
+(26年-04月-19日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -30710,7 +30710,7 @@
           <t>C | 588呎 (2房)
 $1855万
 $31,541/呎
-(21年-10月)</t>
+(21年-10月-03日)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -30718,7 +30718,7 @@
           <t>D | 481呎 (2房)
 $1443万
 $29,993/呎
-(21年-09月)</t>
+(21年-09月-03日)</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -30726,7 +30726,7 @@
           <t>E | 523呎 (2房)
 $1546万
 $29,562/呎
-(21年-09月)</t>
+(21年-09月-22日)</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
@@ -30734,7 +30734,7 @@
           <t>F | 465呎 (2房)
 $1239万
 $26,653/呎
-(23年-12月)</t>
+(23年-12月-18日)</t>
         </is>
       </c>
     </row>
@@ -30749,7 +30749,7 @@
           <t>A | 1420呎 (4+房)
 $5910万
 $41,618/呎
-(26年-02月)</t>
+(26年-02月-25日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -30757,7 +30757,7 @@
           <t>B | 941呎 (3房)
 $3829万
 $40,689/呎
-(21年-10月)</t>
+(21年-10月-06日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -30765,7 +30765,7 @@
           <t>C | 589呎 (2房)
 $1907万
 $32,375/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -30773,7 +30773,7 @@
           <t>D | 481呎 (2房)
 $1510万
 $31,398/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -30781,7 +30781,7 @@
           <t>E | 523呎 (2房)
 $1590万
 $30,396/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr">
@@ -30789,7 +30789,7 @@
           <t>F | 465呎 (2房)
 $1549万
 $33,315/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
     </row>
@@ -30804,7 +30804,7 @@
           <t>A | 1420呎 (4+房)
 $5214万
 $36,721/呎
-(25年-09月)</t>
+(25年-09月-25日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -30812,7 +30812,7 @@
           <t>B | 942呎 (3房)
 $3732万
 $39,616/呎
-(21年-09月)</t>
+(21年-09月-17日)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -30820,7 +30820,7 @@
           <t>C | 588呎 (2房)
 $1844万
 $31,354/呎
-(21年-10月)</t>
+(21年-10月-06日)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -30828,7 +30828,7 @@
           <t>D | 481呎 (2房)
 $1434万
 $29,813/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -30836,7 +30836,7 @@
           <t>E | 523呎 (2房)
 $1537万
 $29,386/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr">
@@ -30844,7 +30844,7 @@
           <t>F | 465呎 (2房)
 $1471万
 $31,635/呎
-(21年-10月)</t>
+(21年-10月-04日)</t>
         </is>
       </c>
     </row>
@@ -30867,7 +30867,7 @@
           <t>B | 941呎 (3房)
 $3519万
 $37,396/呎
-(21年-10月)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -30875,7 +30875,7 @@
           <t>C | 588呎 (2房)
 $1924万
 $32,724/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -30883,7 +30883,7 @@
           <t>D | 481呎 (2房)
 $1497万
 $31,119/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
@@ -30891,7 +30891,7 @@
           <t>E | 523呎 (2房)
 $1394万
 $26,657/呎
-(24年-05月)</t>
+(24年-05月-05日)</t>
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr">
@@ -30899,7 +30899,7 @@
           <t>F | 464呎 (2房)
 $1535万
 $33,091/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
     </row>
@@ -30922,7 +30922,7 @@
           <t>B | 942呎 (3房)
 $3677万
 $39,029/呎
-(21年-10月)</t>
+(21年-10月-14日)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -30930,7 +30930,7 @@
           <t>C | 588呎 (2房)
 $1918万
 $32,627/呎
-(21年-09月)</t>
+(21年-09月-10日)</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">
@@ -30938,7 +30938,7 @@
           <t>D | 481呎 (2房)
 $1492万
 $31,024/呎
-(21年-09月)</t>
+(21年-09月-23日)</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
@@ -30946,7 +30946,7 @@
           <t>E | 523呎 (2房)
 $1599万
 $30,580/呎
-(21年-09月)</t>
+(21年-09月-23日)</t>
         </is>
       </c>
       <c r="G27" s="20" t="inlineStr">
@@ -30954,7 +30954,7 @@
           <t>F | 465呎 (2房)
 $1531万
 $32,921/呎
-(21年-10月)</t>
+(21年-10月-06日)</t>
         </is>
       </c>
     </row>
@@ -30969,7 +30969,7 @@
           <t>A | 1352呎 (4+房)
 $5556万
 $41,091/呎
-(25年-05月)</t>
+(25年-05月-25日)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -30977,7 +30977,7 @@
           <t>B | 882呎 (3房)
 $3902万
 $44,240/呎
-(25年-09月)</t>
+(25年-09月-10日)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -30985,7 +30985,7 @@
           <t>C | 549呎 (2房)
 $1867万
 $34,001/呎
-(22年-02月)</t>
+(22年-02月-15日)</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
@@ -30993,7 +30993,7 @@
           <t>D | 443呎 (2房)
 $1462万
 $33,000/呎
-(22年-02月)</t>
+(22年-02月-15日)</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
@@ -31001,7 +31001,7 @@
           <t>E | 485呎 (2房)
 $1600万
 $33,000/呎
-(22年-02月)</t>
+(22年-02月-16日)</t>
         </is>
       </c>
       <c r="G28" s="20" t="inlineStr">
@@ -31009,7 +31009,7 @@
           <t>F | 425呎 (2房)
 $1424万
 $33,500/呎
-(22年-02月)</t>
+(22年-02月-15日)</t>
         </is>
       </c>
     </row>
@@ -31193,7 +31193,7 @@
           <t>A | 955呎 (3房)
 $4102万
 $42,955/呎
-(22年-02月)</t>
+(22年-02月-16日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -31201,7 +31201,7 @@
           <t>B | 842呎 (3房)
 $3245万
 $38,536/呎
-(22年-03月)</t>
+(22年-03月-09日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -31209,7 +31209,7 @@
           <t>C | 850呎 (3房)
 $3476万
 $40,892/呎
-(23年-02月)</t>
+(23年-02月-26日)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -31217,7 +31217,7 @@
           <t>D | 920呎 (3房)
 $3630万
 $39,454/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="F6" s="20" t="inlineStr">
@@ -31225,7 +31225,7 @@
           <t>E | 341呎 (1房)
 $1257万
 $36,874/呎
-(21年-09月)</t>
+(21年-09月-03日)</t>
         </is>
       </c>
       <c r="G6" s="20" t="inlineStr">
@@ -31233,7 +31233,7 @@
           <t>F | 604呎 (2房)
 $1782万
 $29,499/呎
-(24年-04月)</t>
+(24年-04月-01日)</t>
         </is>
       </c>
     </row>
@@ -31248,7 +31248,7 @@
           <t>A | 955呎 (3房)
 $3249万
 $34,024/呎
-(23年-12月)</t>
+(23年-12月-21日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -31256,7 +31256,7 @@
           <t>B | 842呎 (3房)
 $3222万
 $38,268/呎
-(23年-03月)</t>
+(23年-03月-07日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -31264,7 +31264,7 @@
           <t>C | 850呎 (3房)
 $3452万
 $40,608/呎
-(23年-02月)</t>
+(23年-02月-26日)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -31272,7 +31272,7 @@
           <t>D | 920呎 (3房)
 $3605万
 $39,180/呎
-(21年-10月)</t>
+(21年-10月-03日)</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
@@ -31280,7 +31280,7 @@
           <t>E | 341呎 (1房)
 $1194万
 $35,012/呎
-(21年-09月)</t>
+(21年-09月-03日)</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
@@ -31288,7 +31288,7 @@
           <t>F | 604呎 (2房)
 $1776万
 $29,409/呎
-(24年-09月)</t>
+(24年-09月-29日)</t>
         </is>
       </c>
     </row>
@@ -31303,7 +31303,7 @@
           <t>A | 955呎 (3房)
 $3227万
 $33,788/呎
-(23年-12月)</t>
+(23年-12月-19日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -31311,7 +31311,7 @@
           <t>B | 842呎 (3房)
 $3200万
 $38,002/呎
-(22年-02月)</t>
+(22年-02月-10日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -31319,7 +31319,7 @@
           <t>C | 850呎 (3房)
 $2871万
 $33,772/呎
-(23年-12月)</t>
+(23年-12月-28日)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -31327,7 +31327,7 @@
           <t>D | 920呎 (3房)
 $3580万
 $38,908/呎
-(21年-10月)</t>
+(21年-10月-03日)</t>
         </is>
       </c>
       <c r="F8" s="20" t="inlineStr">
@@ -31335,7 +31335,7 @@
           <t>E | 341呎 (1房)
 $1190万
 $34,904/呎
-(21年-09月)</t>
+(21年-09月-29日)</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -31343,7 +31343,7 @@
           <t>F | 604呎 (2房)
 $1771万
 $29,323/呎
-(24年-05月)</t>
+(24年-05月-01日)</t>
         </is>
       </c>
     </row>
@@ -31358,7 +31358,7 @@
           <t>A | 955呎 (3房)
 $3634万
 $38,051/呎
-(21年-09月)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -31366,7 +31366,7 @@
           <t>B | 842呎 (3房)
 $3289万
 $39,056/呎
-(21年-09月)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -31374,7 +31374,7 @@
           <t>C | 850呎 (3房)
 $3233万
 $38,031/呎
-(21年-09月)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -31382,7 +31382,7 @@
           <t>D | 921呎 (3房)
 $3487万
 $37,861/呎
-(21年-09月)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -31390,7 +31390,7 @@
           <t>E | 341呎 (1房)
 $1246万
 $36,544/呎
-(21年-09月)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -31398,7 +31398,7 @@
           <t>F | 604呎 (2房)
 $1766万
 $29,234/呎
-(24年-07月)</t>
+(24年-07月-04日)</t>
         </is>
       </c>
     </row>
@@ -31413,7 +31413,7 @@
           <t>A | 955呎 (3房)
 $3609万
 $37,786/呎
-(21年-09月)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -31421,7 +31421,7 @@
           <t>B | 842呎 (3房)
 $3110万
 $36,938/呎
-(21年-09月)</t>
+(21年-09月-20日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -31429,7 +31429,7 @@
           <t>C | 850呎 (3房)
 $3210万
 $37,767/呎
-(21年-09月)</t>
+(21年-09月-20日)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -31437,7 +31437,7 @@
           <t>D | 921呎 (3房)
 $3298万
 $35,807/呎
-(21年-09月)</t>
+(21年-09月-20日)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -31445,7 +31445,7 @@
           <t>E | 341呎 (1房)
 $1183万
 $34,698/呎
-(21年-09月)</t>
+(21年-09月-29日)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -31453,7 +31453,7 @@
           <t>F | 604呎 (2房)
 $1760万
 $29,147/呎
-(24年-04月)</t>
+(24年-04月-08日)</t>
         </is>
       </c>
     </row>
@@ -31468,7 +31468,7 @@
           <t>A | 955呎 (3房)
 $3584万
 $37,524/呎
-(21年-09月)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -31476,7 +31476,7 @@
           <t>B | 842呎 (3房)
 $3185万
 $37,827/呎
-(21年-09月)</t>
+(21年-09月-29日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -31484,7 +31484,7 @@
           <t>C | 850呎 (3房)
 $3188万
 $37,504/呎
-(21年-09月)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -31492,7 +31492,7 @@
           <t>D | 921呎 (3房)
 $3439万
 $37,337/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
@@ -31500,7 +31500,7 @@
           <t>E | 341呎 (1房)
 $1180万
 $34,597/呎
-(21年-09月)</t>
+(21年-09月-16日)</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
@@ -31508,7 +31508,7 @@
           <t>F | 604呎 (2房)
 $1755万
 $29,060/呎
-(24年-04月)</t>
+(24年-04月-07日)</t>
         </is>
       </c>
     </row>
@@ -31523,7 +31523,7 @@
           <t>A | 955呎 (3房)
 $3559万
 $37,263/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -31531,7 +31531,7 @@
           <t>B | 842呎 (3房)
 $3067万
 $36,426/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -31539,7 +31539,7 @@
           <t>C | 850呎 (3房)
 $3166万
 $37,242/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -31547,7 +31547,7 @@
           <t>D | 920呎 (3房)
 $3252万
 $35,349/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
@@ -31555,7 +31555,7 @@
           <t>E | 341呎 (1房)
 $1176万
 $34,494/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="G12" s="20" t="inlineStr">
@@ -31563,7 +31563,7 @@
           <t>F | 604呎 (2房)
 $1750万
 $28,973/呎
-(24年-03月)</t>
+(24年-03月-27日)</t>
         </is>
       </c>
     </row>
@@ -31578,7 +31578,7 @@
           <t>A | 955呎 (3房)
 $3711万
 $38,854/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -31586,7 +31586,7 @@
           <t>B | 842呎 (3房)
 $3046万
 $36,172/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -31594,7 +31594,7 @@
           <t>C | 850呎 (3房)
 $3301万
 $38,834/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -31602,7 +31602,7 @@
           <t>D | 921呎 (3房)
 $3230万
 $35,066/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
@@ -31610,7 +31610,7 @@
           <t>E | 341呎 (1房)
 $1173万
 $34,391/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
@@ -31618,7 +31618,7 @@
           <t>F | 604呎 (2房)
 $2083万
 $34,490/呎
-(22年-02月)</t>
+(22年-02月-24日)</t>
         </is>
       </c>
     </row>
@@ -31633,7 +31633,7 @@
           <t>A | 955呎 (3房)
 $3711万
 $38,854/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -31641,7 +31641,7 @@
           <t>B | 842呎 (3房)
 $3046万
 $36,172/呎
-(21年-10月)</t>
+(21年-10月-04日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -31649,7 +31649,7 @@
           <t>C | 850呎 (3房)
 $3301万
 $38,834/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -31657,7 +31657,7 @@
           <t>D | 921呎 (3房)
 $3341万
 $36,275/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -31665,7 +31665,7 @@
           <t>E | 341呎 (1房)
 $949万
 $27,820/呎
-(24年-02月)</t>
+(24年-02月-06日)</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
@@ -31673,7 +31673,7 @@
           <t>F | 604呎 (2房)
 $1719万
 $28,458/呎
-(24年-03月)</t>
+(24年-03月-25日)</t>
         </is>
       </c>
     </row>
@@ -31688,7 +31688,7 @@
           <t>A | 955呎 (3房)
 $3485万
 $36,493/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -31696,7 +31696,7 @@
           <t>B | 842呎 (3房)
 $3004万
 $35,673/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -31704,7 +31704,7 @@
           <t>C | 850呎 (3房)
 $3100万
 $36,473/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -31712,7 +31712,7 @@
           <t>D | 921呎 (3房)
 $3295万
 $35,774/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
@@ -31720,7 +31720,7 @@
           <t>E | 341呎 (1房)
 $1126万
 $33,021/呎
-(21年-09月)</t>
+(21年-09月-03日)</t>
         </is>
       </c>
       <c r="G15" s="20" t="inlineStr">
@@ -31728,7 +31728,7 @@
           <t>F | 604呎 (2房)
 $1745万
 $28,899/呎
-(24年-04月)</t>
+(24年-04月-01日)</t>
         </is>
       </c>
     </row>
@@ -31743,7 +31743,7 @@
           <t>A | 955呎 (3房)
 $3356万
 $35,141/呎
-(24年-11月)</t>
+(24年-11月-26日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -31751,7 +31751,7 @@
           <t>B | 842呎 (3房)
 $3132万
 $37,196/呎
-(21年-10月)</t>
+(21年-10月-06日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -31759,7 +31759,7 @@
           <t>C | 850呎 (3房)
 $2950万
 $34,706/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -31767,7 +31767,7 @@
           <t>D | 921呎 (3房)
 $2993万
 $32,493/呎
-(24年-02月)</t>
+(24年-02月-19日)</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -31775,7 +31775,7 @@
           <t>E | 341呎 (1房)
 $1123万
 $32,922/呎
-(21年-09月)</t>
+(21年-09月-03日)</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -31783,7 +31783,7 @@
           <t>F | 604呎 (2房)
 $1703万
 $28,203/呎
-(24年-04月)</t>
+(24年-04月-17日)</t>
         </is>
       </c>
     </row>
@@ -31798,7 +31798,7 @@
           <t>A | 955呎 (3房)
 $3403万
 $35,632/呎
-(21年-10月)</t>
+(21年-10月-04日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -31806,7 +31806,7 @@
           <t>B | 842呎 (3房)
 $3025万
 $35,921/呎
-(21年-10月)</t>
+(21年-10月-06日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -31814,7 +31814,7 @@
           <t>C | 850呎 (3房)
 $3122万
 $36,728/呎
-(21年-10月)</t>
+(21年-10月-06日)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -31822,7 +31822,7 @@
           <t>D | 921呎 (3房)
 $3185万
 $34,584/呎
-(21年-09月)</t>
+(21年-09月-29日)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -31830,7 +31830,7 @@
           <t>E | 341呎 (1房)
 $1147万
 $33,644/呎
-(21年-09月)</t>
+(21年-09月-03日)</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -31838,7 +31838,7 @@
           <t>F | 604呎 (2房)
 $1698万
 $28,120/呎
-(24年-04月)</t>
+(24年-04月-16日)</t>
         </is>
       </c>
     </row>
@@ -31853,7 +31853,7 @@
           <t>A | 955呎 (3房)
 $3558万
 $37,253/呎
-(21年-10月)</t>
+(21年-10月-07日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -31861,7 +31861,7 @@
           <t>B | 842呎 (3房)
 $2780万
 $33,017/呎
-(24年-11月)</t>
+(24年-11月-19日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -31869,7 +31869,7 @@
           <t>C | 850呎 (3房)
 $3088万
 $36,328/呎
-(21年-09月)</t>
+(21年-09月-17日)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -31877,7 +31877,7 @@
           <t>D | 920呎 (3房)
 $2922万
 $31,761/呎
-(24年-11月)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -31885,7 +31885,7 @@
           <t>E | 341呎 (1房)
 $1116万
 $32,727/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -31893,7 +31893,7 @@
           <t>F | 604呎 (2房)
 $2123万
 $35,149/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
     </row>
@@ -31908,7 +31908,7 @@
           <t>A | 955呎 (3房)
 $3619万
 $37,897/呎
-(21年-10月)</t>
+(21年-10月-06日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -31916,7 +31916,7 @@
           <t>B | 842呎 (3房)
 $3036万
 $36,051/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -31924,7 +31924,7 @@
           <t>C | 850呎 (3房)
 $3066万
 $36,075/呎
-(21年-10月)</t>
+(21年-10月-06日)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -31932,7 +31932,7 @@
           <t>D | 920呎 (3房)
 $2992万
 $32,517/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -31940,7 +31940,7 @@
           <t>E | 341呎 (1房)
 $1113万
 $32,629/呎
-(21年-09月)</t>
+(21年-09月-03日)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -31948,7 +31948,7 @@
           <t>F | 604呎 (2房)
 $2016万
 $33,374/呎
-(22年-07月)</t>
+(22年-07月-11日)</t>
         </is>
       </c>
     </row>
@@ -31963,7 +31963,7 @@
           <t>A | 955呎 (3房)
 $3423万
 $35,841/呎
-(21年-10月)</t>
+(21年-10月-10日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -31971,7 +31971,7 @@
           <t>B | 842呎 (3房)
 $2843万
 $33,761/呎
-(21年-10月)</t>
+(21年-10月-06日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -31979,7 +31979,7 @@
           <t>C | 850呎 (3房)
 $3045万
 $35,825/呎
-(21年-10月)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -31987,7 +31987,7 @@
           <t>D | 921呎 (3房)
 $3045万
 $33,063/呎
-(21年-09月)</t>
+(21年-09月-03日)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -31995,7 +31995,7 @@
           <t>E | 341呎 (1房)
 $1144万
 $33,547/呎
-(21年-09月)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
@@ -32003,7 +32003,7 @@
           <t>F | 604呎 (2房)
 $1683万
 $27,867/呎
-(24年-03月)</t>
+(24年-03月-26日)</t>
         </is>
       </c>
     </row>
@@ -32018,7 +32018,7 @@
           <t>A | 955呎 (3房)
 $3399万
 $35,592/呎
-(21年-10月)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -32026,7 +32026,7 @@
           <t>B | 842呎 (3房)
 $2823万
 $33,527/呎
-(23年-07月)</t>
+(23年-07月-20日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -32034,7 +32034,7 @@
           <t>C | 850呎 (3房)
 $3175万
 $37,354/呎
-(21年-10月)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
@@ -32042,7 +32042,7 @@
           <t>D | 920呎 (3房)
 $2950万
 $32,066/呎
-(21年-09月)</t>
+(21年-09月-29日)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -32050,7 +32050,7 @@
           <t>E | 341呎 (1房)
 $1106万
 $32,434/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr">
@@ -32058,7 +32058,7 @@
           <t>F | 604呎 (2房)
 $1678万
 $27,785/呎
-(24年-01月)</t>
+(24年-01月-09日)</t>
         </is>
       </c>
     </row>
@@ -32073,7 +32073,7 @@
           <t>A | 955呎 (3房)
 $3363万
 $35,218/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -32081,7 +32081,7 @@
           <t>B | 842呎 (3房)
 $2683万
 $31,860/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -32089,7 +32089,7 @@
           <t>C | 850呎 (3房)
 $2994万
 $35,229/呎
-(21年-09月)</t>
+(21年-09月-16日)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -32097,7 +32097,7 @@
           <t>D | 921呎 (3房)
 $2935万
 $31,872/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -32105,7 +32105,7 @@
           <t>E | 341呎 (1房)
 $1103万
 $32,335/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr">
@@ -32113,7 +32113,7 @@
           <t>F | 604呎 (2房)
 $1998万
 $33,075/呎
-(21年-11月)</t>
+(21年-11月-21日)</t>
         </is>
       </c>
     </row>
@@ -32128,7 +32128,7 @@
           <t>A | 955呎 (3房)
 $3107万
 $32,534/呎
-(24年-03月)</t>
+(24年-03月-27日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -32136,7 +32136,7 @@
           <t>B | 842呎 (3房)
 $2817万
 $33,453/呎
-(21年-09月)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -32144,7 +32144,7 @@
           <t>C | 850呎 (3房)
 $2994万
 $35,229/呎
-(21年-09月)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -32152,7 +32152,7 @@
           <t>D | 921呎 (3房)
 $3082万
 $33,466/呎
-(21年-09月)</t>
+(21年-09月-20日)</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -32160,7 +32160,7 @@
           <t>E | 341呎 (1房)
 $1158万
 $33,952/呎
-(21年-09月)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
@@ -32168,7 +32168,7 @@
           <t>F | 604呎 (2房)
 $1998万
 $33,075/呎
-(22年-01月)</t>
+(22年-01月-24日)</t>
         </is>
       </c>
     </row>
@@ -32183,7 +32183,7 @@
           <t>A | 955呎 (3房)
 $3330万
 $34,868/呎
-(21年-09月)</t>
+(21年-09月-23日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -32191,7 +32191,7 @@
           <t>B | 842呎 (3房)
 $2566万
 $30,476/呎
-(24年-03月)</t>
+(24年-03月-21日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -32199,7 +32199,7 @@
           <t>C | 850呎 (3房)
 $2965万
 $34,879/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -32207,7 +32207,7 @@
           <t>D | 920呎 (3房)
 $2906万
 $31,591/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -32215,7 +32215,7 @@
           <t>E | 341呎 (1房)
 $918万
 $26,920/呎
-(24年-04月)</t>
+(24年-04月-22日)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr">
@@ -32223,7 +32223,7 @@
           <t>F | 604呎 (2房)
 $1663万
 $27,537/呎
-(24年-02月)</t>
+(24年-02月-05日)</t>
         </is>
       </c>
     </row>
@@ -32238,7 +32238,7 @@
           <t>A | 955呎 (3房)
 $3156万
 $33,042/呎
-(21年-09月)</t>
+(21年-09月-23日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -32246,7 +32246,7 @@
           <t>B | 842呎 (3房)
 $2632万
 $31,264/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -32254,7 +32254,7 @@
           <t>C | 850呎 (3房)
 $2809万
 $33,052/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -32262,7 +32262,7 @@
           <t>D | 921呎 (3房)
 $3037万
 $32,970/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -32270,7 +32270,7 @@
           <t>E | 341呎 (1房)
 $1147万
 $33,649/呎
-(21年-09月)</t>
+(21年-09月-23日)</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr">
@@ -32278,7 +32278,7 @@
           <t>F | 604呎 (2房)
 $1658万
 $27,453/呎
-(23年-12月)</t>
+(23年-12月-14日)</t>
         </is>
       </c>
     </row>
@@ -32293,7 +32293,7 @@
           <t>A | 955呎 (3房)
 $3297万
 $34,522/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -32301,7 +32301,7 @@
           <t>B | 842呎 (3房)
 $2619万
 $31,108/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -32309,7 +32309,7 @@
           <t>C | 850呎 (3房)
 $2795万
 $32,887/呎
-(24年-04月)</t>
+(24年-04月-02日)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -32317,7 +32317,7 @@
           <t>D | 921呎 (3房)
 $2878万
 $31,243/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
@@ -32325,7 +32325,7 @@
           <t>E | 341呎 (1房)
 $1090万
 $31,953/呎
-(21年-09月)</t>
+(21年-09月-23日)</t>
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr">
@@ -32333,7 +32333,7 @@
           <t>F | 604呎 (2房)
 $1653万
 $27,371/呎
-(24年-03月)</t>
+(24年-03月-20日)</t>
         </is>
       </c>
     </row>
@@ -32348,7 +32348,7 @@
           <t>A | 955呎 (3房)
 $3037万
 $31,797/呎
-(24年-02月)</t>
+(24年-02月-08日)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -32356,7 +32356,7 @@
           <t>B | 842呎 (3房)
 $2606万
 $30,953/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -32364,7 +32364,7 @@
           <t>C | 850呎 (3房)
 $2926万
 $34,428/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">
@@ -32372,7 +32372,7 @@
           <t>D | 921呎 (3房)
 $2869万
 $31,150/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
@@ -32380,7 +32380,7 @@
           <t>E | 341呎 (1房)
 $1086万
 $31,859/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="G27" s="20" t="inlineStr">
@@ -32388,7 +32388,7 @@
           <t>F | 604呎 (2房)
 $2067万
 $34,215/呎
-(21年-10月)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
     </row>
@@ -32403,7 +32403,7 @@
           <t>A | 955呎 (3房)
 $3027万
 $31,701/呎
-(24年-04月)</t>
+(24年-04月-07日)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -32411,7 +32411,7 @@
           <t>B | 842呎 (3房)
 $2593万
 $30,798/呎
-(21年-09月)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -32419,7 +32419,7 @@
           <t>C | 850呎 (3房)
 $2918万
 $34,325/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
@@ -32427,7 +32427,7 @@
           <t>D | 921呎 (3房)
 $2860万
 $31,057/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
@@ -32435,7 +32435,7 @@
           <t>E | 341呎 (1房)
 $1130万
 $33,150/呎
-(21年-10月)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
       <c r="G28" s="20" t="inlineStr">
@@ -32443,7 +32443,7 @@
           <t>F | 604呎 (2房)
 $1643万
 $27,208/呎
-(24年-04月)</t>
+(24年-04月-04日)</t>
         </is>
       </c>
     </row>
@@ -32458,7 +32458,7 @@
           <t>A | 955呎 (3房)
 $3267万
 $34,212/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
@@ -32466,7 +32466,7 @@
           <t>B | 842呎 (3房)
 $2654万
 $31,516/呎
-(22年-06月)</t>
+(22年-06月-27日)</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
@@ -32474,7 +32474,7 @@
           <t>C | 850呎 (3房)
 $2909万
 $34,223/呎
-(21年-09月)</t>
+(21年-09月-29日)</t>
         </is>
       </c>
       <c r="E29" s="20" t="inlineStr">
@@ -32482,7 +32482,7 @@
           <t>D | 921呎 (3房)
 $2852万
 $30,963/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="F29" s="20" t="inlineStr">
@@ -32490,7 +32490,7 @@
           <t>E | 341呎 (1房)
 $1127万
 $33,048/呎
-(21年-10月)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
       <c r="G29" s="20" t="inlineStr">
@@ -32498,7 +32498,7 @@
           <t>F | 604呎 (2房)
 $2054万
 $34,010/呎
-(21年-12月)</t>
+(21年-12月-15日)</t>
         </is>
       </c>
     </row>
@@ -32513,7 +32513,7 @@
           <t>A | 955呎 (3房)
 $3112万
 $32,583/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr">
@@ -32521,7 +32521,7 @@
           <t>B | 842呎 (3房)
 $2709万
 $32,178/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
@@ -32529,7 +32529,7 @@
           <t>C | 850呎 (3房)
 $2770万
 $32,593/呎
-(21年-10月)</t>
+(21年-10月-04日)</t>
         </is>
       </c>
       <c r="E30" s="20" t="inlineStr">
@@ -32537,7 +32537,7 @@
           <t>D | 921呎 (3房)
 $2923万
 $31,737/呎
-(21年-09月)</t>
+(21年-09月-10日)</t>
         </is>
       </c>
       <c r="F30" s="20" t="inlineStr">
@@ -32545,7 +32545,7 @@
           <t>E | 341呎 (1房)
 $1134万
 $33,253/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="G30" s="20" t="inlineStr">
@@ -32553,7 +32553,7 @@
           <t>F | 604呎 (2房)
 $1634万
 $27,046/呎
-(24年-03月)</t>
+(24年-03月-26日)</t>
         </is>
       </c>
     </row>
@@ -32568,7 +32568,7 @@
           <t>A | 955呎 (3房)
 $3248万
 $34,008/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
@@ -32576,7 +32576,7 @@
           <t>B | 842呎 (3房)
 $2635万
 $31,291/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
@@ -32584,7 +32584,7 @@
           <t>C | 850呎 (3房)
 $2754万
 $32,398/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="E31" s="20" t="inlineStr">
@@ -32592,7 +32592,7 @@
           <t>D | 920呎 (3房)
 $2835万
 $30,810/呎
-(21年-10月)</t>
+(21年-10月-04日)</t>
         </is>
       </c>
       <c r="F31" s="20" t="inlineStr">
@@ -32600,7 +32600,7 @@
           <t>E | 341呎 (1房)
 $1127万
 $33,056/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="G31" s="20" t="inlineStr">
@@ -32608,7 +32608,7 @@
           <t>F | 604呎 (2房)
 $1624万
 $26,885/呎
-(24年-03月)</t>
+(24年-03月-25日)</t>
         </is>
       </c>
     </row>
@@ -32623,7 +32623,7 @@
           <t>A | 955呎 (3房)
 $3084万
 $32,291/呎
-(21年-10月)</t>
+(21年-10月-03日)</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
@@ -32631,7 +32631,7 @@
           <t>B | 842呎 (3房)
 $2606万
 $30,948/呎
-(21年-10月)</t>
+(21年-10月-03日)</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
@@ -32639,7 +32639,7 @@
           <t>C | 850呎 (3房)
 $2746万
 $32,301/呎
-(24年-03月)</t>
+(24年-03月-27日)</t>
         </is>
       </c>
       <c r="E32" s="20" t="inlineStr">
@@ -32647,7 +32647,7 @@
           <t>D | 921呎 (3房)
 $2826万
 $30,685/呎
-(21年-09月)</t>
+(21年-09月-29日)</t>
         </is>
       </c>
       <c r="F32" s="20" t="inlineStr">
@@ -32655,7 +32655,7 @@
           <t>E | 341呎 (1房)
 $1070万
 $31,385/呎
-(21年-10月)</t>
+(21年-10月-06日)</t>
         </is>
       </c>
       <c r="G32" s="20" t="inlineStr">
@@ -32663,7 +32663,7 @@
           <t>F | 604呎 (2房)
 $1619万
 $26,804/呎
-(24年-03月)</t>
+(24年-03月-27日)</t>
         </is>
       </c>
     </row>
@@ -32678,7 +32678,7 @@
           <t>A | 901呎 (3房)
 $3244万
 $36,000/呎
-(22年-02月)</t>
+(22年-02月-10日)</t>
         </is>
       </c>
       <c r="C33" s="20" t="inlineStr">
@@ -32686,7 +32686,7 @@
           <t>B | 797呎 (3房)
 $2778万
 $34,851/呎
-(22年-02月)</t>
+(22年-02月-10日)</t>
         </is>
       </c>
       <c r="D33" s="20" t="inlineStr">
@@ -32694,7 +32694,7 @@
           <t>C | 799呎 (3房)
 $2916万
 $36,500/呎
-(22年-02月)</t>
+(22年-02月-08日)</t>
         </is>
       </c>
       <c r="E33" s="20" t="inlineStr">
@@ -32702,7 +32702,7 @@
           <t>D | 873呎 (3房)
 $3250万
 $37,232/呎
-(22年-02月)</t>
+(22年-02月-10日)</t>
         </is>
       </c>
       <c r="F33" s="20" t="inlineStr">
@@ -32710,7 +32710,7 @@
           <t>E | 320呎 (1房)
 $841万
 $26,287/呎
-(23年-12月)</t>
+(23年-12月-19日)</t>
         </is>
       </c>
       <c r="G33" s="20" t="inlineStr">
@@ -32718,7 +32718,7 @@
           <t>F | 566呎 (2房)
 $1840万
 $32,500/呎
-(22年-04月)</t>
+(22年-04月-13日)</t>
         </is>
       </c>
     </row>
@@ -32875,7 +32875,7 @@
           <t>B | 1431呎 (4+房)
 $6053万
 $42,300/呎
-(25年-07月)</t>
+(25年-07月-14日)</t>
         </is>
       </c>
       <c r="D5" s="23" t="inlineStr">
@@ -32894,10 +32894,59 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 594呎 (2房)
+$1678万
+$28,251/呎
+(24年-05月-26日)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 749呎 (3房)
+$2413万
+$32,213/呎
+(24年-04月-25日)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>E | 553呎 (2房)
+$1726万
+$31,211/呎
+(24年-06月-11日)</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>F | 343呎 (1房)
+$1216万
+$35,464/呎
+(21年-09月-19日)</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr">
+        <is>
+          <t>G | 470呎 (2房)
+$1707万
+$36,317/呎
+(22年-05月-26日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>37&amp;38</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>A | 1235呎 (3房)
 -
@@ -32905,61 +32954,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr"/>
-      <c r="D6" s="21" t="inlineStr"/>
-      <c r="E6" s="21" t="inlineStr"/>
-      <c r="F6" s="21" t="inlineStr"/>
-      <c r="G6" s="21" t="inlineStr"/>
-      <c r="H6" s="21" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr"/>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>B | 594呎 (2房)
-$1678万
-$28,251/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D7" s="20" t="inlineStr">
-        <is>
-          <t>C | 749呎 (3房)
-$2413万
-$32,213/呎
-(24年-04月)</t>
-        </is>
-      </c>
+      <c r="C7" s="21" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr"/>
       <c r="E7" s="21" t="inlineStr"/>
-      <c r="F7" s="20" t="inlineStr">
-        <is>
-          <t>E | 553呎 (2房)
-$1726万
-$31,211/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="G7" s="20" t="inlineStr">
-        <is>
-          <t>F | 343呎 (1房)
-$1216万
-$35,464/呎
-(21年-09月)</t>
-        </is>
-      </c>
-      <c r="H7" s="20" t="inlineStr">
-        <is>
-          <t>G | 470呎 (2房)
-$1707万
-$36,317/呎
-(22年-05月)</t>
-        </is>
-      </c>
+      <c r="F7" s="21" t="inlineStr"/>
+      <c r="G7" s="21" t="inlineStr"/>
+      <c r="H7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -32972,7 +32972,7 @@
           <t>A | 638呎 (2房)
 $2180万
 $34,170/呎
-(21年-10月)</t>
+(21年-10月-03日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -32980,7 +32980,7 @@
           <t>B | 594呎 (2房)
 $1673万
 $28,166/呎
-(24年-05月)</t>
+(24年-05月-26日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -32988,7 +32988,7 @@
           <t>C | 749呎 (3房)
 $2405万
 $32,115/呎
-(24年-05月)</t>
+(24年-05月-01日)</t>
         </is>
       </c>
       <c r="E8" s="21" t="inlineStr"/>
@@ -32997,7 +32997,7 @@
           <t>E | 553呎 (2房)
 $2008万
 $36,302/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -33005,7 +33005,7 @@
           <t>F | 343呎 (1房)
 $1273万
 $37,124/呎
-(21年-10月)</t>
+(21年-10月-04日)</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
@@ -33013,7 +33013,7 @@
           <t>G | 470呎 (2房)
 $1702万
 $36,208/呎
-(22年-05月)</t>
+(22年-05月-25日)</t>
         </is>
       </c>
     </row>
@@ -33028,7 +33028,7 @@
           <t>A | 638呎 (2房)
 $2070万
 $32,446/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -33036,7 +33036,7 @@
           <t>B | 594呎 (2房)
 $1946万
 $32,761/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -33044,7 +33044,7 @@
           <t>C | 749呎 (3房)
 $2398万
 $32,021/呎
-(24年-04月)</t>
+(24年-04月-15日)</t>
         </is>
       </c>
       <c r="E9" s="21" t="inlineStr"/>
@@ -33053,7 +33053,7 @@
           <t>E | 553呎 (2房)
 $2002万
 $36,195/呎
-(21年-10月)</t>
+(21年-10月-03日)</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -33061,7 +33061,7 @@
           <t>F | 343呎 (1房)
 $1270万
 $37,014/呎
-(21年-10月)</t>
+(21年-10月-04日)</t>
         </is>
       </c>
       <c r="H9" s="20" t="inlineStr">
@@ -33069,7 +33069,7 @@
           <t>G | 470呎 (2房)
 $1697万
 $36,099/呎
-(21年-10月)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
     </row>
@@ -33084,7 +33084,7 @@
           <t>A | 638呎 (2房)
 $2063万
 $32,335/呎
-(21年-09月)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -33092,7 +33092,7 @@
           <t>B | 594呎 (2房)
 $1931万
 $32,504/呎
-(21年-10月)</t>
+(21年-10月-04日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -33100,7 +33100,7 @@
           <t>C | 749呎 (3房)
 $2391万
 $31,925/呎
-(24年-04月)</t>
+(24年-04月-01日)</t>
         </is>
       </c>
       <c r="E10" s="21" t="inlineStr"/>
@@ -33109,7 +33109,7 @@
           <t>E | 553呎 (2房)
 $1996万
 $36,088/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -33117,7 +33117,7 @@
           <t>F | 343呎 (1房)
 $1266万
 $36,904/呎
-(21年-10月)</t>
+(21年-10月-04日)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr">
@@ -33125,7 +33125,7 @@
           <t>G | 470呎 (2房)
 $1776万
 $37,791/呎
-(21年-10月)</t>
+(21年-10月-10日)</t>
         </is>
       </c>
     </row>
@@ -33140,7 +33140,7 @@
           <t>A | 638呎 (2房)
 $2057万
 $32,237/呎
-(21年-09月)</t>
+(21年-09月-29日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -33148,7 +33148,7 @@
           <t>B | 594呎 (2房)
 $1833万
 $30,865/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -33156,7 +33156,7 @@
           <t>C | 749呎 (3房)
 $2384万
 $31,828/呎
-(23年-12月)</t>
+(23年-12月-20日)</t>
         </is>
       </c>
       <c r="E11" s="21" t="inlineStr"/>
@@ -33165,7 +33165,7 @@
           <t>E | 553呎 (2房)
 $1895万
 $34,265/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
@@ -33173,7 +33173,7 @@
           <t>F | 343呎 (1房)
 $1202万
 $35,039/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="H11" s="20" t="inlineStr">
@@ -33181,7 +33181,7 @@
           <t>G | 470呎 (2房)
 $1687万
 $35,884/呎
-(21年-10月)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
     </row>
@@ -33196,7 +33196,7 @@
           <t>A | 638呎 (2房)
 $1953万
 $30,609/呎
-(21年-09月)</t>
+(21年-09月-20日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -33204,7 +33204,7 @@
           <t>B | 594呎 (2房)
 $1828万
 $30,770/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -33212,7 +33212,7 @@
           <t>C | 749呎 (3房)
 $2377万
 $31,733/呎
-(24年-03月)</t>
+(24年-03月-27日)</t>
         </is>
       </c>
       <c r="E12" s="21" t="inlineStr"/>
@@ -33221,7 +33221,7 @@
           <t>E | 553呎 (2房)
 $1889万
 $34,164/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="G12" s="20" t="inlineStr">
@@ -33229,7 +33229,7 @@
           <t>F | 343呎 (1房)
 $1004万
 $29,259/呎
-(24年-04月)</t>
+(24年-04月-16日)</t>
         </is>
       </c>
       <c r="H12" s="20" t="inlineStr">
@@ -33237,7 +33237,7 @@
           <t>G | 470呎 (2房)
 $1408万
 $29,963/呎
-(24年-03月)</t>
+(24年-03月-27日)</t>
         </is>
       </c>
     </row>
@@ -33252,7 +33252,7 @@
           <t>A | 638呎 (2房)
 $1947万
 $30,519/呎
-(21年-09月)</t>
+(21年-09月-23日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -33260,7 +33260,7 @@
           <t>B | 594呎 (2房)
 $1640万
 $27,611/呎
-(24年-04月)</t>
+(24年-04月-21日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -33268,7 +33268,7 @@
           <t>C | 749呎 (3房)
 $2971万
 $39,666/呎
-(22年-01月)</t>
+(22年-01月-21日)</t>
         </is>
       </c>
       <c r="E13" s="21" t="inlineStr"/>
@@ -33277,7 +33277,7 @@
           <t>E | 553呎 (2房)
 $1884万
 $34,063/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
@@ -33285,7 +33285,7 @@
           <t>F | 343呎 (1房)
 $1254万
 $36,573/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="H13" s="20" t="inlineStr">
@@ -33293,7 +33293,7 @@
           <t>G | 470呎 (2房)
 $1404万
 $29,874/呎
-(24年-03月)</t>
+(24年-03月-19日)</t>
         </is>
       </c>
     </row>
@@ -33308,7 +33308,7 @@
           <t>A | 638呎 (2房)
 $1941万
 $30,428/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -33316,7 +33316,7 @@
           <t>B | 594呎 (2房)
 $1908万
 $32,117/呎
-(21年-10月)</t>
+(21年-10月-04日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -33324,7 +33324,7 @@
           <t>C | 749呎 (3房)
 $2363万
 $31,545/呎
-(24年-03月)</t>
+(24年-03月-27日)</t>
         </is>
       </c>
       <c r="E14" s="21" t="inlineStr"/>
@@ -33333,7 +33333,7 @@
           <t>E | 553呎 (2房)
 $1878万
 $33,959/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
@@ -33341,7 +33341,7 @@
           <t>F | 343呎 (1房)
 $1251万
 $36,465/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="H14" s="20" t="inlineStr">
@@ -33349,7 +33349,7 @@
           <t>G | 470呎 (2房)
 $1400万
 $29,784/呎
-(24年-04月)</t>
+(24年-04月-09日)</t>
         </is>
       </c>
     </row>
@@ -33364,7 +33364,7 @@
           <t>A | 638呎 (2房)
 $1913万
 $29,979/呎
-(21年-09月)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -33372,7 +33372,7 @@
           <t>B | 594呎 (2房)
 $1861万
 $31,329/呎
-(21年-09月)</t>
+(21年-09月-29日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -33380,7 +33380,7 @@
           <t>C | 749呎 (3房)
 $2339万
 $31,223/呎
-(24年-04月)</t>
+(24年-04月-09日)</t>
         </is>
       </c>
       <c r="E15" s="21" t="inlineStr"/>
@@ -33389,7 +33389,7 @@
           <t>E | 553呎 (2房)
 $1850万
 $33,458/呎
-(21年-10月)</t>
+(21年-10月-03日)</t>
         </is>
       </c>
       <c r="G15" s="20" t="inlineStr">
@@ -33397,7 +33397,7 @@
           <t>F | 343呎 (1房)
 $1174万
 $34,216/呎
-(21年-10月)</t>
+(21年-10月-03日)</t>
         </is>
       </c>
       <c r="H15" s="20" t="inlineStr">
@@ -33405,7 +33405,7 @@
           <t>G | 470呎 (2房)
 $1647万
 $35,038/呎
-(21年-10月)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
     </row>
@@ -33420,7 +33420,7 @@
           <t>A | 638呎 (2房)
 $1996万
 $31,289/呎
-(21年-09月)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -33428,7 +33428,7 @@
           <t>B | 594呎 (2房)
 $1762万
 $29,661/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -33436,7 +33436,7 @@
           <t>C | 749呎 (3房)
 $2673万
 $35,686/呎
-(21年-10月)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
       <c r="E16" s="21" t="inlineStr"/>
@@ -33445,7 +33445,7 @@
           <t>E | 553呎 (2房)
 $1839万
 $33,257/呎
-(21年-10月)</t>
+(21年-10月-03日)</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -33453,7 +33453,7 @@
           <t>F | 343呎 (1房)
 $977万
 $28,484/呎
-(24年-04月)</t>
+(24年-04月-22日)</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr">
@@ -33461,7 +33461,7 @@
           <t>G | 470呎 (2房)
 $1637万
 $34,829/呎
-(22年-05月)</t>
+(22年-05月-23日)</t>
         </is>
       </c>
     </row>
@@ -33476,7 +33476,7 @@
           <t>A | 638呎 (2房)
 $1990万
 $31,197/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -33484,7 +33484,7 @@
           <t>B | 594呎 (2房)
 $1844万
 $31,049/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -33492,7 +33492,7 @@
           <t>C | 749呎 (3房)
 $2665万
 $35,579/呎
-(21年-09月)</t>
+(21年-09月-17日)</t>
         </is>
       </c>
       <c r="E17" s="21" t="inlineStr"/>
@@ -33501,7 +33501,7 @@
           <t>E | 553呎 (2房)
 $1925万
 $34,815/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -33509,7 +33509,7 @@
           <t>F | 343呎 (1房)
 $1221万
 $35,603/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr">
@@ -33517,7 +33517,7 @@
           <t>G | 470呎 (2房)
 $1632万
 $34,725/呎
-(21年-10月)</t>
+(21年-10月-10日)</t>
         </is>
       </c>
     </row>
@@ -33532,7 +33532,7 @@
           <t>A | 638呎 (2房)
 $1965万
 $30,797/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -33540,7 +33540,7 @@
           <t>B | 594呎 (2房)
 $1839万
 $30,957/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -33548,7 +33548,7 @@
           <t>C | 749呎 (3房)
 $2723万
 $36,359/呎
-(21年-10月)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
       <c r="E18" s="21" t="inlineStr"/>
@@ -33557,7 +33557,7 @@
           <t>E | 553呎 (2房)
 $1828万
 $33,060/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -33565,7 +33565,7 @@
           <t>F | 343呎 (1房)
 $1160万
 $33,808/呎
-(21年-10月)</t>
+(21年-10月-04日)</t>
         </is>
       </c>
       <c r="H18" s="20" t="inlineStr">
@@ -33573,7 +33573,7 @@
           <t>G | 470呎 (2房)
 $1627万
 $34,620/呎
-(22年-01月)</t>
+(22年-01月-20日)</t>
         </is>
       </c>
     </row>
@@ -33588,7 +33588,7 @@
           <t>A | 638呎 (2房)
 $1866万
 $29,243/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -33596,7 +33596,7 @@
           <t>B | 594呎 (2房)
 $1746万
 $29,395/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -33604,7 +33604,7 @@
           <t>C | 749呎 (3房)
 $2649万
 $35,367/呎
-(21年-10月)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
       <c r="E19" s="21" t="inlineStr"/>
@@ -33613,7 +33613,7 @@
           <t>E | 553呎 (2房)
 $1823万
 $32,961/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -33621,7 +33621,7 @@
           <t>F | 343呎 (1房)
 $1214万
 $35,393/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="H19" s="20" t="inlineStr">
@@ -33629,7 +33629,7 @@
           <t>G | 470呎 (2房)
 $1622万
 $34,517/呎
-(21年-10月)</t>
+(21年-10月-10日)</t>
         </is>
       </c>
     </row>
@@ -33644,7 +33644,7 @@
           <t>A | 638呎 (2房)
 $1860万
 $29,155/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -33652,7 +33652,7 @@
           <t>B | 594呎 (2房)
 $1795万
 $30,224/呎
-(21年-09月)</t>
+(21年-09月-23日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -33660,7 +33660,7 @@
           <t>C | 749呎 (3房)
 $2641万
 $35,262/呎
-(21年-10月)</t>
+(21年-10月-06日)</t>
         </is>
       </c>
       <c r="E20" s="21" t="inlineStr"/>
@@ -33669,7 +33669,7 @@
           <t>E | 553呎 (2房)
 $1800万
 $32,547/呎
-(21年-09月)</t>
+(21年-09月-20日)</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
@@ -33677,7 +33677,7 @@
           <t>F | 343呎 (1房)
 $1210万
 $35,290/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="H20" s="20" t="inlineStr">
@@ -33685,7 +33685,7 @@
           <t>G | 470呎 (2房)
 $1668万
 $35,489/呎
-(21年-10月)</t>
+(21年-10月-06日)</t>
         </is>
       </c>
     </row>
@@ -33700,7 +33700,7 @@
           <t>A | 638呎 (2房)
 $1854万
 $29,067/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -33708,7 +33708,7 @@
           <t>B | 594呎 (2房)
 $1736万
 $29,219/呎
-(21年-09月)</t>
+(21年-09月-23日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -33716,7 +33716,7 @@
           <t>C | 749呎 (3房)
 $2765万
 $36,912/呎
-(21年-10月)</t>
+(21年-10月-07日)</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr"/>
@@ -33725,7 +33725,7 @@
           <t>E | 553呎 (2房)
 $1615万
 $29,205/呎
-(24年-04月)</t>
+(24年-04月-18日)</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr">
@@ -33733,7 +33733,7 @@
           <t>F | 343呎 (1房)
 $963万
 $28,064/呎
-(24年-04月)</t>
+(24年-04月-09日)</t>
         </is>
       </c>
       <c r="H21" s="20" t="inlineStr">
@@ -33741,7 +33741,7 @@
           <t>G | 470呎 (2房)
 $1693万
 $36,027/呎
-(21年-10月)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
     </row>
@@ -33756,7 +33756,7 @@
           <t>A | 638呎 (2房)
 $1849万
 $28,979/呎
-(21年-09月)</t>
+(21年-09月-29日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -33764,7 +33764,7 @@
           <t>B | 594呎 (2房)
 $1817万
 $30,588/呎
-(21年-09月)</t>
+(21年-09月-29日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -33772,7 +33772,7 @@
           <t>C | 749呎 (3房)
 $2625万
 $35,050/呎
-(21年-10月)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
       <c r="E22" s="21" t="inlineStr"/>
@@ -33781,7 +33781,7 @@
           <t>E | 553呎 (2房)
 $1879万
 $33,971/呎
-(21年-09月)</t>
+(21年-09月-29日)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr">
@@ -33789,7 +33789,7 @@
           <t>F | 343呎 (1房)
 $1146万
 $33,406/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="H22" s="20" t="inlineStr">
@@ -33797,7 +33797,7 @@
           <t>G | 470呎 (2房)
 $1688万
 $35,920/呎
-(21年-10月)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
     </row>
@@ -33812,7 +33812,7 @@
           <t>A | 638呎 (2房)
 $1936万
 $30,339/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -33820,7 +33820,7 @@
           <t>B | 594呎 (2房)
 $1725万
 $29,045/呎
-(21年-09月)</t>
+(21年-09月-03日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -33828,7 +33828,7 @@
           <t>C | 749呎 (3房)
 $2617万
 $34,946/呎
-(21年-10月)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
       <c r="E23" s="21" t="inlineStr"/>
@@ -33837,7 +33837,7 @@
           <t>E | 553呎 (2房)
 $1784万
 $32,255/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
@@ -33845,7 +33845,7 @@
           <t>F | 343呎 (1房)
 $1142万
 $33,308/呎
-(21年-10月)</t>
+(21年-10月-04日)</t>
         </is>
       </c>
       <c r="H23" s="20" t="inlineStr">
@@ -33853,7 +33853,7 @@
           <t>G | 470呎 (2房)
 $1343万
 $28,565/呎
-(25年-11月)</t>
+(25年-11月-27日)</t>
         </is>
       </c>
     </row>
@@ -33868,7 +33868,7 @@
           <t>A | 638呎 (2房)
 $1843万
 $28,894/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -33876,7 +33876,7 @@
           <t>B | 594呎 (2房)
 $1779万
 $29,953/呎
-(21年-09月)</t>
+(21年-09月-23日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -33884,7 +33884,7 @@
           <t>C | 749呎 (3房)
 $2748万
 $36,693/呎
-(21年-10月)</t>
+(21年-10月-10日)</t>
         </is>
       </c>
       <c r="E24" s="21" t="inlineStr"/>
@@ -33893,7 +33893,7 @@
           <t>E | 553呎 (2房)
 $1784万
 $32,255/呎
-(21年-09月)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr">
@@ -33901,7 +33901,7 @@
           <t>F | 343呎 (1房)
 $1142万
 $33,308/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="H24" s="20" t="inlineStr">
@@ -33909,7 +33909,7 @@
           <t>G | 470呎 (2房)
 $1653万
 $35,173/呎
-(21年-10月)</t>
+(21年-10月-10日)</t>
         </is>
       </c>
     </row>
@@ -33924,7 +33924,7 @@
           <t>A | 638呎 (2房)
 $1832万
 $28,721/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -33932,7 +33932,7 @@
           <t>B | 594呎 (2房)
 $1715万
 $28,873/呎
-(21年-09月)</t>
+(21年-09月-23日)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -33940,7 +33940,7 @@
           <t>C | 749呎 (3房)
 $2602万
 $34,736/呎
-(21年-10月)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
       <c r="E25" s="21" t="inlineStr"/>
@@ -33949,7 +33949,7 @@
           <t>E | 553呎 (2房)
 $1773万
 $32,062/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr">
@@ -33957,7 +33957,7 @@
           <t>F | 343呎 (1房)
 $1136万
 $33,108/呎
-(21年-09月)</t>
+(21年-09月-10日)</t>
         </is>
       </c>
       <c r="H25" s="20" t="inlineStr">
@@ -33965,7 +33965,7 @@
           <t>G | 470呎 (2房)
 $1593万
 $33,903/呎
-(21年-10月)</t>
+(21年-10月-06日)</t>
         </is>
       </c>
     </row>
@@ -33980,7 +33980,7 @@
           <t>A | 638呎 (2房)
 $1873万
 $29,350/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -33988,7 +33988,7 @@
           <t>B | 594呎 (2房)
 $1753万
 $29,506/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -33996,7 +33996,7 @@
           <t>C | 749呎 (3房)
 $2724万
 $36,364/呎
-(21年-10月)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
       <c r="E26" s="21" t="inlineStr"/>
@@ -34005,7 +34005,7 @@
           <t>E | 553呎 (2房)
 $1591万
 $28,770/呎
-(24年-04月)</t>
+(24年-04月-17日)</t>
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr">
@@ -34013,7 +34013,7 @@
           <t>F | 343呎 (1房)
 $1132万
 $33,008/呎
-(21年-10月)</t>
+(21年-10月-03日)</t>
         </is>
       </c>
       <c r="H26" s="20" t="inlineStr">
@@ -34021,7 +34021,7 @@
           <t>G | 470呎 (2房)
 $1330万
 $28,308/呎
-(24年-03月)</t>
+(24年-03月-14日)</t>
         </is>
       </c>
     </row>
@@ -34036,7 +34036,7 @@
           <t>A | 638呎 (2房)
 $1867万
 $29,263/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -34044,7 +34044,7 @@
           <t>B | 594呎 (2房)
 $1790万
 $30,135/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -34052,7 +34052,7 @@
           <t>C | 749呎 (3房)
 $2586万
 $34,529/呎
-(21年-10月)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
       <c r="E27" s="21" t="inlineStr"/>
@@ -34061,7 +34061,7 @@
           <t>E | 553呎 (2房)
 $1851万
 $33,463/呎
-(21年-09月)</t>
+(21年-09月-03日)</t>
         </is>
       </c>
       <c r="G27" s="20" t="inlineStr">
@@ -34069,7 +34069,7 @@
           <t>F | 343呎 (1房)
 $1157万
 $33,732/呎
-(21年-10月)</t>
+(21年-10月-06日)</t>
         </is>
       </c>
       <c r="H27" s="20" t="inlineStr">
@@ -34077,7 +34077,7 @@
           <t>G | 470呎 (2房)
 $1584万
 $33,699/呎
-(21年-10月)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
     </row>
@@ -34092,7 +34092,7 @@
           <t>A | 638呎 (2房)
 $1861万
 $29,176/呎
-(21年-09月)</t>
+(21年-09月-03日)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -34100,7 +34100,7 @@
           <t>B | 594呎 (2房)
 $1700万
 $28,614/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -34108,7 +34108,7 @@
           <t>C | 749呎 (3房)
 $2707万
 $36,148/呎
-(21年-10月)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
       <c r="E28" s="21" t="inlineStr"/>
@@ -34117,7 +34117,7 @@
           <t>E | 553呎 (2房)
 $1757万
 $31,776/呎
-(21年-09月)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="G28" s="20" t="inlineStr">
@@ -34125,7 +34125,7 @@
           <t>F | 343呎 (1房)
 $1125万
 $32,809/呎
-(21年-10月)</t>
+(21年-10月-03日)</t>
         </is>
       </c>
       <c r="H28" s="20" t="inlineStr">
@@ -34133,7 +34133,7 @@
           <t>G | 470呎 (2房)
 $1579万
 $33,598/呎
-(21年-10月)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
     </row>
@@ -34148,7 +34148,7 @@
           <t>A | 638呎 (2房)
 $1901万
 $29,799/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
@@ -34156,7 +34156,7 @@
           <t>B | 594呎 (2房)
 $1525万
 $25,674/呎
-(24年-04月)</t>
+(24年-04月-16日)</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
@@ -34164,7 +34164,7 @@
           <t>C | 749呎 (3房)
 $2699万
 $36,040/呎
-(21年-10月)</t>
+(21年-10月-10日)</t>
         </is>
       </c>
       <c r="E29" s="21" t="inlineStr"/>
@@ -34173,7 +34173,7 @@
           <t>E | 553呎 (2房)
 $1752万
 $31,680/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="G29" s="20" t="inlineStr">
@@ -34181,7 +34181,7 @@
           <t>F | 343呎 (1房)
 $1122万
 $32,714/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="H29" s="20" t="inlineStr">
@@ -34189,7 +34189,7 @@
           <t>G | 470呎 (2房)
 $1574万
 $33,500/呎
-(22年-02月)</t>
+(22年-02月-15日)</t>
         </is>
       </c>
     </row>
@@ -34204,7 +34204,7 @@
           <t>A | 638呎 (2房)
 $1895万
 $29,709/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr">
@@ -34212,7 +34212,7 @@
           <t>B | 594呎 (2房)
 $1690万
 $28,443/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
@@ -34220,7 +34220,7 @@
           <t>C | 749呎 (3房)
 $2691万
 $35,932/呎
-(21年-09月)</t>
+(21年-09月-17日)</t>
         </is>
       </c>
       <c r="E30" s="21" t="inlineStr"/>
@@ -34229,7 +34229,7 @@
           <t>E | 553呎 (2房)
 $1834万
 $33,164/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="G30" s="20" t="inlineStr">
@@ -34237,7 +34237,7 @@
           <t>F | 343呎 (1房)
 $1175万
 $34,249/呎
-(22年-02月)</t>
+(22年-02月-21日)</t>
         </is>
       </c>
       <c r="H30" s="20" t="inlineStr">
@@ -34245,7 +34245,7 @@
           <t>G | 470呎 (2房)
 $1315万
 $27,972/呎
-(23年-12月)</t>
+(23年-12月-17日)</t>
         </is>
       </c>
     </row>
@@ -34260,7 +34260,7 @@
           <t>A | 638呎 (2房)
 $1895万
 $29,709/呎
-(21年-09月)</t>
+(21年-09月-23日)</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
@@ -34268,7 +34268,7 @@
           <t>B | 544呎 (2房)
 $1578万
 $29,012/呎
-(21年-09月)</t>
+(21年-09月-29日)</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
@@ -34276,7 +34276,7 @@
           <t>C | 469呎 (2房)
 $1491万
 $31,792/呎
-(21年-09月)</t>
+(21年-09月-29日)</t>
         </is>
       </c>
       <c r="E31" s="20" t="inlineStr">
@@ -34284,7 +34284,7 @@
           <t>D | 335呎 (1房)
 $1158万
 $34,553/呎
-(21年-09月)</t>
+(21年-09月-29日)</t>
         </is>
       </c>
       <c r="F31" s="20" t="inlineStr">
@@ -34292,7 +34292,7 @@
           <t>E | 553呎 (2房)
 $1572万
 $28,426/呎
-(24年-06月)</t>
+(24年-06月-26日)</t>
         </is>
       </c>
       <c r="G31" s="20" t="inlineStr">
@@ -34300,7 +34300,7 @@
           <t>F | 343呎 (1房)
 $934万
 $27,238/呎
-(24年-03月)</t>
+(24年-03月-24日)</t>
         </is>
       </c>
       <c r="H31" s="20" t="inlineStr">
@@ -34308,7 +34308,7 @@
           <t>G | 470呎 (2房)
 $1311万
 $27,888/呎
-(24年-02月)</t>
+(24年-02月-20日)</t>
         </is>
       </c>
     </row>
@@ -34323,7 +34323,7 @@
           <t>A | 638呎 (2房)
 $1794万
 $28,125/呎
-(21年-09月)</t>
+(21年-09月-20日)</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
@@ -34331,7 +34331,7 @@
           <t>B | 544呎 (2房)
 $1647万
 $30,280/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
@@ -34339,7 +34339,7 @@
           <t>C | 470呎 (2房)
 $1556万
 $33,110/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="E32" s="20" t="inlineStr">
@@ -34347,7 +34347,7 @@
           <t>D | 335呎 (1房)
 $913万
 $27,262/呎
-(24年-04月)</t>
+(24年-04月-14日)</t>
         </is>
       </c>
       <c r="F32" s="20" t="inlineStr">
@@ -34355,7 +34355,7 @@
           <t>E | 553呎 (2房)
 $1766万
 $31,931/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="G32" s="20" t="inlineStr">
@@ -34363,7 +34363,7 @@
           <t>F | 343呎 (1房)
 $1103万
 $32,170/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="H32" s="20" t="inlineStr">
@@ -34371,7 +34371,7 @@
           <t>G | 470呎 (2房)
 $1303万
 $27,722/呎
-(24年-04月)</t>
+(24年-04月-01日)</t>
         </is>
       </c>
     </row>
@@ -34386,7 +34386,7 @@
           <t>A | 638呎 (2房)
 $1610万
 $25,236/呎
-(25年-07月)</t>
+(25年-07月-13日)</t>
         </is>
       </c>
       <c r="C33" s="20" t="inlineStr">
@@ -34394,7 +34394,7 @@
           <t>B | 545呎 (2房)
 $1642万
 $30,134/呎
-(21年-09月)</t>
+(21年-09月-10日)</t>
         </is>
       </c>
       <c r="D33" s="20" t="inlineStr">
@@ -34402,7 +34402,7 @@
           <t>C | 469呎 (2房)
 $1478万
 $31,509/呎
-(21年-10月)</t>
+(21年-10月-04日)</t>
         </is>
       </c>
       <c r="E33" s="20" t="inlineStr">
@@ -34410,7 +34410,7 @@
           <t>D | 335呎 (1房)
 $1110万
 $33,143/呎
-(21年-09月)</t>
+(21年-09月-10日)</t>
         </is>
       </c>
       <c r="F33" s="20" t="inlineStr">
@@ -34418,7 +34418,7 @@
           <t>E | 553呎 (2房)
 $1531万
 $27,680/呎
-(26年-01月)</t>
+(26年-01月-14日)</t>
         </is>
       </c>
       <c r="G33" s="20" t="inlineStr">
@@ -34426,7 +34426,7 @@
           <t>F | 343呎 (1房)
 $1144万
 $33,348/呎
-(21年-10月)</t>
+(21年-10月-07日)</t>
         </is>
       </c>
       <c r="H33" s="20" t="inlineStr">
@@ -34434,7 +34434,7 @@
           <t>G | 470呎 (2房)
 $1299万
 $27,638/呎
-(24年-04月)</t>
+(24年-04月-09日)</t>
         </is>
       </c>
     </row>
@@ -34449,7 +34449,7 @@
           <t>A | 598呎 (2房)
 $2003万
 $33,500/呎
-(22年-02月)</t>
+(22年-02月-14日)</t>
         </is>
       </c>
       <c r="C34" s="20" t="inlineStr">
@@ -34457,7 +34457,7 @@
           <t>B | 506呎 (2房)
 $1594万
 $31,500/呎
-(22年-02月)</t>
+(22年-02月-14日)</t>
         </is>
       </c>
       <c r="D34" s="20" t="inlineStr">
@@ -34465,7 +34465,7 @@
           <t>C | 436呎 (2房)
 $1405万
 $32,226/呎
-(21年-10月)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
       <c r="E34" s="21" t="inlineStr"/>
@@ -34476,7 +34476,7 @@
           <t>G | 442呎 (2房)
 $1222万
 $27,637/呎
-(23年-12月)</t>
+(23年-12月-18日)</t>
         </is>
       </c>
     </row>

--- a/web/files/港岛-香港仔及鸭脷洲-扬海.xlsx
+++ b/web/files/港岛-香港仔及鸭脷洲-扬海.xlsx
@@ -32894,11 +32894,32 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>37&amp;38</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>A | 1235呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr"/>
+      <c r="E6" s="21" t="inlineStr"/>
+      <c r="F6" s="21" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr"/>
+      <c r="H6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>B | 594呎 (2房)
 $1678万
@@ -32906,7 +32927,7 @@
 (24年-05月-26日)</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 749呎 (3房)
 $2413万
@@ -32914,8 +32935,8 @@
 (24年-04月-25日)</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr"/>
-      <c r="F6" s="20" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr"/>
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>E | 553呎 (2房)
 $1726万
@@ -32923,7 +32944,7 @@
 (24年-06月-11日)</t>
         </is>
       </c>
-      <c r="G6" s="20" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>F | 343呎 (1房)
 $1216万
@@ -32931,7 +32952,7 @@
 (21年-09月-19日)</t>
         </is>
       </c>
-      <c r="H6" s="20" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>G | 470呎 (2房)
 $1707万
@@ -32939,27 +32960,6 @@
 (22年-05月-26日)</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>37&amp;38</t>
-        </is>
-      </c>
-      <c r="B7" s="23" t="inlineStr">
-        <is>
-          <t>A | 1235呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="21" t="inlineStr"/>
-      <c r="D7" s="21" t="inlineStr"/>
-      <c r="E7" s="21" t="inlineStr"/>
-      <c r="F7" s="21" t="inlineStr"/>
-      <c r="G7" s="21" t="inlineStr"/>
-      <c r="H7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">

--- a/web/files/港岛-香港仔及鸭脷洲-扬海.xlsx
+++ b/web/files/港岛-香港仔及鸭脷洲-扬海.xlsx
@@ -32894,10 +32894,59 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 594呎 (2房)
+$1678万
+$28,251/呎
+(24年-05月-26日)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 749呎 (3房)
+$2413万
+$32,213/呎
+(24年-04月-25日)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>E | 553呎 (2房)
+$1726万
+$31,211/呎
+(24年-06月-11日)</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>F | 343呎 (1房)
+$1216万
+$35,464/呎
+(21年-09月-19日)</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr">
+        <is>
+          <t>G | 470呎 (2房)
+$1707万
+$36,317/呎
+(22年-05月-26日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>37&amp;38</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>A | 1235呎 (3房)
 -
@@ -32905,61 +32954,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr"/>
-      <c r="D6" s="21" t="inlineStr"/>
-      <c r="E6" s="21" t="inlineStr"/>
-      <c r="F6" s="21" t="inlineStr"/>
-      <c r="G6" s="21" t="inlineStr"/>
-      <c r="H6" s="21" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr"/>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>B | 594呎 (2房)
-$1678万
-$28,251/呎
-(24年-05月-26日)</t>
-        </is>
-      </c>
-      <c r="D7" s="20" t="inlineStr">
-        <is>
-          <t>C | 749呎 (3房)
-$2413万
-$32,213/呎
-(24年-04月-25日)</t>
-        </is>
-      </c>
+      <c r="C7" s="21" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr"/>
       <c r="E7" s="21" t="inlineStr"/>
-      <c r="F7" s="20" t="inlineStr">
-        <is>
-          <t>E | 553呎 (2房)
-$1726万
-$31,211/呎
-(24年-06月-11日)</t>
-        </is>
-      </c>
-      <c r="G7" s="20" t="inlineStr">
-        <is>
-          <t>F | 343呎 (1房)
-$1216万
-$35,464/呎
-(21年-09月-19日)</t>
-        </is>
-      </c>
-      <c r="H7" s="20" t="inlineStr">
-        <is>
-          <t>G | 470呎 (2房)
-$1707万
-$36,317/呎
-(22年-05月-26日)</t>
-        </is>
-      </c>
+      <c r="F7" s="21" t="inlineStr"/>
+      <c r="G7" s="21" t="inlineStr"/>
+      <c r="H7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
